--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CBB56E-EEEE-4D6A-BFAF-FBC884E0C0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EF44C9-87A2-46FB-8921-69653B2FF9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1072,10 +1072,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="N11" t="s">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="O11" t="s">
         <v>173</v>
@@ -1134,10 +1134,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="N12" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="O12" t="s">
         <v>173</v>
@@ -1196,10 +1196,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="O13" t="s">
         <v>173</v>
@@ -1320,10 +1320,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="N15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="O15" t="s">
         <v>173</v>
@@ -1382,10 +1382,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="N16" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="O16" t="s">
         <v>173</v>
@@ -1444,10 +1444,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="N17" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="O17" t="s">
         <v>173</v>
@@ -1506,10 +1506,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="N18" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="O18" t="s">
         <v>173</v>
@@ -1568,10 +1568,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="N19" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="O19" t="s">
         <v>173</v>
@@ -1630,10 +1630,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="N20" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="O20" t="s">
         <v>173</v>
@@ -1692,10 +1692,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="N21" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O21" t="s">
         <v>173</v>
@@ -1754,10 +1754,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="N22" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="O22" t="s">
         <v>173</v>
@@ -1816,10 +1816,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="N23" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="O23" t="s">
         <v>173</v>
@@ -1878,10 +1878,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="N24" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="O24" t="s">
         <v>173</v>
@@ -1940,10 +1940,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="N25" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O25" t="s">
         <v>173</v>
@@ -1978,10 +1978,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="N26" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="O26" t="s">
         <v>173</v>
@@ -2016,10 +2016,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="N27" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="O27" t="s">
         <v>173</v>
@@ -2054,10 +2054,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N28" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="O28" t="s">
         <v>173</v>
@@ -2092,10 +2092,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="N29" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="O29" t="s">
         <v>173</v>
@@ -2130,10 +2130,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="N30" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="O30" t="s">
         <v>173</v>
@@ -2168,10 +2168,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="N31" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="O31" t="s">
         <v>173</v>
@@ -2206,10 +2206,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N32" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="O32" t="s">
         <v>173</v>
@@ -2244,10 +2244,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="N33" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="O33" t="s">
         <v>173</v>
@@ -2282,10 +2282,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="O34" t="s">
         <v>173</v>
@@ -2320,10 +2320,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="N35" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="O35" t="s">
         <v>173</v>
@@ -2346,10 +2346,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O36" t="s">
         <v>173</v>
@@ -2372,10 +2372,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="N37" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="O37" t="s">
         <v>173</v>
@@ -2398,10 +2398,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="N38" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="O38" t="s">
         <v>173</v>
@@ -2424,10 +2424,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="N39" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="O39" t="s">
         <v>173</v>
@@ -2450,10 +2450,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="N40" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="O40" t="s">
         <v>173</v>
@@ -2476,10 +2476,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="N41" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O41" t="s">
         <v>173</v>
@@ -2502,10 +2502,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="N42" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="O42" t="s">
         <v>173</v>
@@ -2528,10 +2528,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="N43" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="O43" t="s">
         <v>173</v>
@@ -2554,10 +2554,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="N44" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="O44" t="s">
         <v>173</v>
@@ -2580,10 +2580,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="N45" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="O45" t="s">
         <v>173</v>
@@ -2606,10 +2606,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="N46" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="O46" t="s">
         <v>173</v>
@@ -2632,10 +2632,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="N47" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="O47" t="s">
         <v>173</v>
@@ -2658,10 +2658,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N48" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="O48" t="s">
         <v>173</v>
@@ -2684,10 +2684,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="N49" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="O49" t="s">
         <v>173</v>
@@ -2710,10 +2710,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="N50" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="O50" t="s">
         <v>173</v>
@@ -2736,10 +2736,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="N51" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="O51" t="s">
         <v>173</v>
@@ -2762,10 +2762,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="N52" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="O52" t="s">
         <v>173</v>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EF44C9-87A2-46FB-8921-69653B2FF9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DEAE81-BD6E-445D-99A7-2D23CB07CE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -559,13 +559,13 @@
     <t>at grid node - Murray_AUS</t>
   </si>
   <si>
+    <t>BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - BrokenHill_AUS</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - BrokenHill_AUS</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1072,13 +1072,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="N11" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="O11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1134,13 +1134,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="N12" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="O12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1196,13 +1196,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="N13" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="O13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1258,13 +1258,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1320,13 +1320,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="N15" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="O15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1382,13 +1382,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="N16" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="O16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1444,13 +1444,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N17" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1506,13 +1506,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="N18" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="O18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1568,13 +1568,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="N19" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="O19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1630,13 +1630,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="N20" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="O20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1692,13 +1692,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="N21" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="O21" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1754,13 +1754,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="N22" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="O22" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1816,13 +1816,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="N23" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="O23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1878,13 +1878,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="N24" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="O24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1940,13 +1940,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="N25" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="O25" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
@@ -1978,13 +1978,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="N26" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="O26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
@@ -2016,13 +2016,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="N27" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="O27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
@@ -2054,13 +2054,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="N28" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="O28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
@@ -2092,13 +2092,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="N29" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="O29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
@@ -2130,13 +2130,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="N30" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="O30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
@@ -2168,13 +2168,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="O31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
@@ -2206,13 +2206,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="N32" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
@@ -2244,13 +2244,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="N33" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="O33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
@@ -2282,13 +2282,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N34" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="O34" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
@@ -2320,13 +2320,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="N35" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="O35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
@@ -2346,13 +2346,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="N36" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="O36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
@@ -2372,13 +2372,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="N37" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="O37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
@@ -2398,13 +2398,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="N38" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="O38" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
@@ -2424,13 +2424,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N39" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="O39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
@@ -2450,13 +2450,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="N40" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="O40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
@@ -2476,13 +2476,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="N41" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="O41" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
@@ -2502,13 +2502,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="N42" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="O42" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
@@ -2528,13 +2528,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="N43" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="O43" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
@@ -2560,7 +2560,7 @@
         <v>109</v>
       </c>
       <c r="O44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
@@ -2580,13 +2580,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="N45" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="O45" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
@@ -2606,13 +2606,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N46" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="O46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
@@ -2632,13 +2632,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="N47" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="O47" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
@@ -2658,13 +2658,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="N48" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="O48" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -2684,13 +2684,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="N49" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="O49" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -2710,13 +2710,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="N50" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="O50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -2736,13 +2736,13 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="N51" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="O51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -2762,13 +2762,13 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="N52" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="O52" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DEAE81-BD6E-445D-99A7-2D23CB07CE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C44D91-DA1F-4F95-8BDA-BAB9765B462B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="182">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -334,10 +334,10 @@
     <t>at grid node - Calvale_AUS</t>
   </si>
   <si>
-    <t>w229759860-220_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - w229759860-220_AUS</t>
+    <t>Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Chalumbin_AUS</t>
   </si>
   <si>
     <t>Perth_AUS</t>
@@ -376,10 +376,10 @@
     <t>at grid node - SouthMorang_AUS</t>
   </si>
   <si>
-    <t>Blackwall_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Blackwall_AUS</t>
+    <t>Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Brisbane_AUS</t>
   </si>
   <si>
     <t>SydneyWest_AUS</t>
@@ -400,54 +400,66 @@
     <t>at grid node - Kalgoorlie_AUS</t>
   </si>
   <si>
+    <t>Dubbo_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Dubbo_AUS</t>
+  </si>
+  <si>
+    <t>TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>Sheffield_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Sheffield_AUS</t>
+  </si>
+  <si>
+    <t>Strathmore_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Strathmore_AUS</t>
+  </si>
+  <si>
+    <t>Wagga_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Wagga_AUS</t>
+  </si>
+  <si>
+    <t>AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>CalliopeRiver_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - CalliopeRiver_AUS</t>
+  </si>
+  <si>
+    <t>Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Hazelwood_AUS</t>
+  </si>
+  <si>
     <t>MountPiper_AUS</t>
   </si>
   <si>
     <t>at grid node - MountPiper_AUS</t>
   </si>
   <si>
-    <t>TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>Sheffield_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Sheffield_AUS</t>
-  </si>
-  <si>
-    <t>Strathmore_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Strathmore_AUS</t>
-  </si>
-  <si>
-    <t>Wagga_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Wagga_AUS</t>
-  </si>
-  <si>
-    <t>AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>CalliopeRiver_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - CalliopeRiver_AUS</t>
-  </si>
-  <si>
-    <t>Hazelwood_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Hazelwood_AUS</t>
-  </si>
-  <si>
     <t>Bouldercombe_AUS</t>
   </si>
   <si>
@@ -499,73 +511,73 @@
     <t>at grid node - Nebo_AUS</t>
   </si>
   <si>
+    <t>Morawa_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Morawa_AUS</t>
+  </si>
+  <si>
+    <t>Balranald_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Balranald_AUS</t>
+  </si>
+  <si>
+    <t>Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>UpperTumut_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - UpperTumut_AUS</t>
+  </si>
+  <si>
+    <t>Horsham_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Horsham_AUS</t>
+  </si>
+  <si>
+    <t>Rowville_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Rowville_AUS</t>
+  </si>
+  <si>
+    <t>Merredin_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Merredin_AUS</t>
+  </si>
+  <si>
+    <t>GinGin_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - GinGin_AUS</t>
+  </si>
+  <si>
     <t>Yandin_AUS</t>
   </si>
   <si>
     <t>at grid node - Yandin_AUS</t>
   </si>
   <si>
-    <t>Balranald_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Balranald_AUS</t>
-  </si>
-  <si>
-    <t>Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>UpperTumut_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - UpperTumut_AUS</t>
-  </si>
-  <si>
-    <t>Horsham_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Horsham_AUS</t>
-  </si>
-  <si>
-    <t>Rowville_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Rowville_AUS</t>
-  </si>
-  <si>
-    <t>Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>Merredin_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Merredin_AUS</t>
-  </si>
-  <si>
-    <t>GinGin_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - GinGin_AUS</t>
-  </si>
-  <si>
     <t>Murray_AUS</t>
   </si>
   <si>
     <t>at grid node - Murray_AUS</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
     <t>BrokenHill_AUS</t>
   </si>
   <si>
     <t>at grid node - BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -940,7 +952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:Y52"/>
+  <dimension ref="B3:Y55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
@@ -1060,25 +1072,25 @@
         <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s">
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="N11" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="O11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1090,7 +1102,7 @@
         <v>101</v>
       </c>
       <c r="T11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V11" t="s">
         <v>86</v>
@@ -1102,7 +1114,7 @@
         <v>101</v>
       </c>
       <c r="Y11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
@@ -1122,25 +1134,25 @@
         <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L12" t="s">
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="N12" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="O12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1152,7 +1164,7 @@
         <v>113</v>
       </c>
       <c r="T12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V12" t="s">
         <v>86</v>
@@ -1164,7 +1176,7 @@
         <v>113</v>
       </c>
       <c r="Y12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
@@ -1190,7 +1202,7 @@
         <v>103</v>
       </c>
       <c r="J13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L13" t="s">
         <v>86</v>
@@ -1202,31 +1214,31 @@
         <v>115</v>
       </c>
       <c r="O13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
       </c>
       <c r="R13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="T13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V13" t="s">
         <v>86</v>
       </c>
       <c r="W13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="X13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Y13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
@@ -1252,43 +1264,43 @@
         <v>88</v>
       </c>
       <c r="J14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L14" t="s">
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="O14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
       </c>
       <c r="R14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="S14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="T14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V14" t="s">
         <v>86</v>
       </c>
       <c r="W14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="X14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="Y14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
@@ -1314,43 +1326,43 @@
         <v>91</v>
       </c>
       <c r="J15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L15" t="s">
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="N15" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="O15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
       </c>
       <c r="R15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="S15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="T15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V15" t="s">
         <v>86</v>
       </c>
       <c r="W15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="X15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
@@ -1376,43 +1388,43 @@
         <v>93</v>
       </c>
       <c r="J16" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L16" t="s">
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="N16" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="O16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
       </c>
       <c r="R16" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="S16" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="T16" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V16" t="s">
         <v>86</v>
       </c>
       <c r="W16" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="X16" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="Y16" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
@@ -1438,19 +1450,19 @@
         <v>95</v>
       </c>
       <c r="J17" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L17" t="s">
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="N17" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="O17" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1462,7 +1474,7 @@
         <v>111</v>
       </c>
       <c r="T17" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V17" t="s">
         <v>86</v>
@@ -1474,7 +1486,7 @@
         <v>111</v>
       </c>
       <c r="Y17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
@@ -1500,43 +1512,43 @@
         <v>97</v>
       </c>
       <c r="J18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L18" t="s">
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="N18" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="O18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
       </c>
       <c r="R18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="S18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="T18" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V18" t="s">
         <v>86</v>
       </c>
       <c r="W18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="X18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Y18" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
@@ -1562,43 +1574,43 @@
         <v>99</v>
       </c>
       <c r="J19" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L19" t="s">
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="N19" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="O19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
       </c>
       <c r="R19" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="S19" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="T19" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V19" t="s">
         <v>86</v>
       </c>
       <c r="W19" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="X19" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="Y19" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
@@ -1624,43 +1636,43 @@
         <v>101</v>
       </c>
       <c r="J20" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L20" t="s">
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N20" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="O20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
       </c>
       <c r="R20" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="S20" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="T20" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V20" t="s">
         <v>86</v>
       </c>
       <c r="W20" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="X20" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="Y20" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
@@ -1686,43 +1698,43 @@
         <v>105</v>
       </c>
       <c r="J21" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L21" t="s">
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="N21" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="O21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
       </c>
       <c r="R21" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="S21" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="T21" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V21" t="s">
         <v>86</v>
       </c>
       <c r="W21" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="X21" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="Y21" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
@@ -1748,43 +1760,43 @@
         <v>107</v>
       </c>
       <c r="J22" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L22" t="s">
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N22" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="O22" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
       </c>
       <c r="R22" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="S22" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="T22" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V22" t="s">
         <v>86</v>
       </c>
       <c r="W22" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="X22" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="Y22" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
@@ -1810,43 +1822,43 @@
         <v>109</v>
       </c>
       <c r="J23" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L23" t="s">
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="N23" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="O23" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
       </c>
       <c r="R23" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="S23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="T23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="V23" t="s">
         <v>86</v>
       </c>
       <c r="W23" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="X23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="Y23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
@@ -1872,42 +1884,18 @@
         <v>111</v>
       </c>
       <c r="J24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L24" t="s">
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N24" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="O24" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>86</v>
-      </c>
-      <c r="R24" t="s">
-        <v>132</v>
-      </c>
-      <c r="S24" t="s">
-        <v>133</v>
-      </c>
-      <c r="T24" t="s">
-        <v>176</v>
-      </c>
-      <c r="V24" t="s">
-        <v>86</v>
-      </c>
-      <c r="W24" t="s">
-        <v>132</v>
-      </c>
-      <c r="X24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y24" t="s">
         <v>177</v>
       </c>
     </row>
@@ -1934,19 +1922,19 @@
         <v>113</v>
       </c>
       <c r="J25" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L25" t="s">
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="N25" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="O25" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
@@ -1972,19 +1960,19 @@
         <v>115</v>
       </c>
       <c r="J26" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L26" t="s">
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="N26" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="O26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
@@ -2010,19 +1998,19 @@
         <v>117</v>
       </c>
       <c r="J27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L27" t="s">
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="N27" t="s">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="O27" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
@@ -2048,19 +2036,19 @@
         <v>119</v>
       </c>
       <c r="J28" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L28" t="s">
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="N28" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="O28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
@@ -2086,19 +2074,19 @@
         <v>121</v>
       </c>
       <c r="J29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L29" t="s">
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="N29" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="O29" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
@@ -2124,19 +2112,19 @@
         <v>123</v>
       </c>
       <c r="J30" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L30" t="s">
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="N30" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="O30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
@@ -2162,19 +2150,19 @@
         <v>125</v>
       </c>
       <c r="J31" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L31" t="s">
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="N31" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="O31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
@@ -2194,25 +2182,25 @@
         <v>86</v>
       </c>
       <c r="H32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J32" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L32" t="s">
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="N32" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="O32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
@@ -2238,19 +2226,19 @@
         <v>131</v>
       </c>
       <c r="J33" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L33" t="s">
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N33" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
@@ -2276,19 +2264,19 @@
         <v>133</v>
       </c>
       <c r="J34" t="s">
+        <v>142</v>
+      </c>
+      <c r="L34" t="s">
+        <v>86</v>
+      </c>
+      <c r="M34" t="s">
         <v>138</v>
       </c>
-      <c r="L34" t="s">
-        <v>86</v>
-      </c>
-      <c r="M34" t="s">
-        <v>141</v>
-      </c>
       <c r="N34" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
@@ -2308,77 +2296,101 @@
         <v>86</v>
       </c>
       <c r="H35" t="s">
+        <v>134</v>
+      </c>
+      <c r="I35" t="s">
+        <v>135</v>
+      </c>
+      <c r="J35" t="s">
+        <v>142</v>
+      </c>
+      <c r="L35" t="s">
+        <v>86</v>
+      </c>
+      <c r="M35" t="s">
+        <v>108</v>
+      </c>
+      <c r="N35" t="s">
+        <v>109</v>
+      </c>
+      <c r="O35" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" t="s">
         <v>139</v>
       </c>
-      <c r="I35" t="s">
+      <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
+        <v>86</v>
+      </c>
+      <c r="H36" t="s">
+        <v>143</v>
+      </c>
+      <c r="I36" t="s">
+        <v>144</v>
+      </c>
+      <c r="J36" t="s">
+        <v>142</v>
+      </c>
+      <c r="L36" t="s">
+        <v>86</v>
+      </c>
+      <c r="M36" t="s">
+        <v>169</v>
+      </c>
+      <c r="N36" t="s">
+        <v>170</v>
+      </c>
+      <c r="O36" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" t="s">
         <v>140</v>
       </c>
-      <c r="J35" t="s">
-        <v>138</v>
-      </c>
-      <c r="L35" t="s">
-        <v>86</v>
-      </c>
-      <c r="M35" t="s">
-        <v>104</v>
-      </c>
-      <c r="N35" t="s">
-        <v>105</v>
-      </c>
-      <c r="O35" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="G36" t="s">
-        <v>86</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="D37" t="s">
         <v>141</v>
       </c>
-      <c r="I36" t="s">
-        <v>142</v>
-      </c>
-      <c r="J36" t="s">
-        <v>138</v>
-      </c>
-      <c r="L36" t="s">
-        <v>86</v>
-      </c>
-      <c r="M36" t="s">
-        <v>112</v>
-      </c>
-      <c r="N36" t="s">
-        <v>113</v>
-      </c>
-      <c r="O36" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="E37" t="s">
+        <v>89</v>
+      </c>
       <c r="G37" t="s">
         <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L37" t="s">
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="N37" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="O37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
@@ -2386,25 +2398,25 @@
         <v>86</v>
       </c>
       <c r="H38" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="I38" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="J38" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L38" t="s">
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="N38" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="O38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
@@ -2418,19 +2430,19 @@
         <v>148</v>
       </c>
       <c r="J39" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L39" t="s">
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="N39" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="O39" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
@@ -2444,19 +2456,19 @@
         <v>150</v>
       </c>
       <c r="J40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s">
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="N40" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="O40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
@@ -2470,7 +2482,7 @@
         <v>152</v>
       </c>
       <c r="J41" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L41" t="s">
         <v>86</v>
@@ -2482,7 +2494,7 @@
         <v>121</v>
       </c>
       <c r="O41" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
@@ -2496,19 +2508,19 @@
         <v>154</v>
       </c>
       <c r="J42" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L42" t="s">
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="N42" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="O42" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
@@ -2522,19 +2534,19 @@
         <v>156</v>
       </c>
       <c r="J43" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s">
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="N43" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="O43" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
@@ -2548,19 +2560,19 @@
         <v>158</v>
       </c>
       <c r="J44" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L44" t="s">
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="N44" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="O44" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
@@ -2574,19 +2586,19 @@
         <v>160</v>
       </c>
       <c r="J45" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L45" t="s">
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N45" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="O45" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
@@ -2600,19 +2612,19 @@
         <v>162</v>
       </c>
       <c r="J46" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L46" t="s">
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="N46" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="O46" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
@@ -2626,19 +2638,19 @@
         <v>164</v>
       </c>
       <c r="J47" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L47" t="s">
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
       <c r="N47" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="O47" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
@@ -2646,13 +2658,13 @@
         <v>86</v>
       </c>
       <c r="H48" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="I48" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="J48" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L48" t="s">
         <v>86</v>
@@ -2664,7 +2676,7 @@
         <v>107</v>
       </c>
       <c r="O48" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -2672,25 +2684,25 @@
         <v>86</v>
       </c>
       <c r="H49" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I49" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J49" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L49" t="s">
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="N49" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="O49" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -2698,25 +2710,25 @@
         <v>86</v>
       </c>
       <c r="H50" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="I50" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="J50" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L50" t="s">
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N50" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="O50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -2730,19 +2742,19 @@
         <v>170</v>
       </c>
       <c r="J51" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L51" t="s">
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="N51" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="O51" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -2756,19 +2768,85 @@
         <v>172</v>
       </c>
       <c r="J52" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L52" t="s">
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="N52" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O52" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G53" t="s">
+        <v>86</v>
+      </c>
+      <c r="H53" t="s">
+        <v>173</v>
+      </c>
+      <c r="I53" t="s">
+        <v>174</v>
+      </c>
+      <c r="J53" t="s">
+        <v>142</v>
+      </c>
+      <c r="L53" t="s">
+        <v>86</v>
+      </c>
+      <c r="M53" t="s">
+        <v>151</v>
+      </c>
+      <c r="N53" t="s">
+        <v>152</v>
+      </c>
+      <c r="O53" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G54" t="s">
+        <v>86</v>
+      </c>
+      <c r="H54" t="s">
         <v>175</v>
+      </c>
+      <c r="I54" t="s">
+        <v>176</v>
+      </c>
+      <c r="J54" t="s">
+        <v>142</v>
+      </c>
+      <c r="L54" t="s">
+        <v>86</v>
+      </c>
+      <c r="M54" t="s">
+        <v>96</v>
+      </c>
+      <c r="N54" t="s">
+        <v>97</v>
+      </c>
+      <c r="O54" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L55" t="s">
+        <v>86</v>
+      </c>
+      <c r="M55" t="s">
+        <v>163</v>
+      </c>
+      <c r="N55" t="s">
+        <v>164</v>
+      </c>
+      <c r="O55" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C44D91-DA1F-4F95-8BDA-BAB9765B462B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9552BB5F-0D84-45C4-86AD-674D7F4D3D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -571,13 +571,13 @@
     <t>at grid node - Murray_AUS</t>
   </si>
   <si>
+    <t>BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - BrokenHill_AUS</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - BrokenHill_AUS</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1084,13 +1084,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="N11" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="O11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1146,13 +1146,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="O12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1214,7 +1214,7 @@
         <v>115</v>
       </c>
       <c r="O13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1270,13 +1270,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="N14" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="O14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1332,13 +1332,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="O15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1394,13 +1394,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="N16" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="O16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1456,13 +1456,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="N17" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="O17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1518,13 +1518,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="N18" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="O18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1580,13 +1580,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="N19" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="O19" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1642,13 +1642,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="N20" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="O20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1704,13 +1704,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="N21" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="O21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1766,13 +1766,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="N22" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="O22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1828,13 +1828,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="N23" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="O23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1896,7 +1896,7 @@
         <v>154</v>
       </c>
       <c r="O24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
@@ -1928,13 +1928,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="N25" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="O25" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
@@ -1966,13 +1966,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="N26" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="O26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
@@ -2010,7 +2010,7 @@
         <v>101</v>
       </c>
       <c r="O27" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
@@ -2042,13 +2042,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="N28" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="O28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
@@ -2080,13 +2080,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="N29" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="O29" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
@@ -2118,13 +2118,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O30" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
@@ -2156,13 +2156,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="N31" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="O31" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
@@ -2194,13 +2194,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="N32" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="O32" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
@@ -2232,13 +2232,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="N33" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="O33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
@@ -2270,13 +2270,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="N34" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="O34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
@@ -2308,13 +2308,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="N35" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="O35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
@@ -2346,13 +2346,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="N36" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="O36" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
@@ -2384,13 +2384,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="N37" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="O37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
@@ -2410,13 +2410,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="N38" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="O38" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
@@ -2436,13 +2436,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="N39" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="O39" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
@@ -2462,13 +2462,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="N40" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="O40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
@@ -2488,13 +2488,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="N41" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="O41" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
@@ -2514,13 +2514,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="N42" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="O42" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
@@ -2540,13 +2540,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="N43" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="O43" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
@@ -2566,13 +2566,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="N44" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="O44" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
@@ -2592,13 +2592,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="N45" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="O45" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
@@ -2624,7 +2624,7 @@
         <v>141</v>
       </c>
       <c r="O46" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
@@ -2644,13 +2644,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="N47" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="O47" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
@@ -2670,13 +2670,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N48" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O48" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -2696,13 +2696,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="N49" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="O49" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -2722,13 +2722,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="N50" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="O50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -2748,13 +2748,13 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="N51" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O51" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -2774,13 +2774,13 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="N52" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="O52" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -2800,13 +2800,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="N53" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="O53" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -2826,13 +2826,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>96</v>
+        <v>171</v>
       </c>
       <c r="N54" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="O54" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -2840,13 +2840,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="N55" t="s">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="O55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9552BB5F-0D84-45C4-86AD-674D7F4D3D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33C4BAF-07A6-4AC5-BFB1-016E23C6023C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="181">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t>ELE</t>
-  </si>
-  <si>
-    <t>NCAP_DRATE</t>
   </si>
   <si>
     <t>EN[_]Hydro*</t>
@@ -957,20 +954,20 @@
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -978,1875 +975,1875 @@
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
         <v>71</v>
       </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" t="s">
         <v>71</v>
       </c>
-      <c r="I10" t="s">
-        <v>72</v>
-      </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" t="s">
         <v>71</v>
       </c>
-      <c r="N10" t="s">
-        <v>72</v>
-      </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R10" t="s">
+        <v>70</v>
+      </c>
+      <c r="S10" t="s">
         <v>71</v>
       </c>
-      <c r="S10" t="s">
-        <v>72</v>
-      </c>
       <c r="T10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W10" t="s">
+        <v>70</v>
+      </c>
+      <c r="X10" t="s">
         <v>71</v>
       </c>
-      <c r="X10" t="s">
-        <v>72</v>
-      </c>
       <c r="Y10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
         <v>86</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>87</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>88</v>
       </c>
-      <c r="E11" t="s">
-        <v>89</v>
-      </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" t="s">
         <v>128</v>
       </c>
-      <c r="I11" t="s">
-        <v>129</v>
-      </c>
       <c r="J11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M11" t="s">
+        <v>176</v>
+      </c>
+      <c r="N11" t="s">
         <v>177</v>
       </c>
-      <c r="N11" t="s">
-        <v>178</v>
-      </c>
       <c r="O11" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" t="s">
+        <v>99</v>
+      </c>
+      <c r="S11" t="s">
+        <v>100</v>
+      </c>
+      <c r="T11" t="s">
         <v>179</v>
       </c>
-      <c r="Q11" t="s">
-        <v>86</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="V11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W11" t="s">
+        <v>99</v>
+      </c>
+      <c r="X11" t="s">
         <v>100</v>
       </c>
-      <c r="S11" t="s">
-        <v>101</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="Y11" t="s">
         <v>180</v>
-      </c>
-      <c r="V11" t="s">
-        <v>86</v>
-      </c>
-      <c r="W11" t="s">
-        <v>100</v>
-      </c>
-      <c r="X11" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
         <v>90</v>
       </c>
-      <c r="D12" t="s">
-        <v>91</v>
-      </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" t="s">
         <v>136</v>
       </c>
-      <c r="I12" t="s">
-        <v>137</v>
-      </c>
       <c r="J12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M12" t="s">
+        <v>150</v>
+      </c>
+      <c r="N12" t="s">
         <v>151</v>
       </c>
-      <c r="N12" t="s">
-        <v>152</v>
-      </c>
       <c r="O12" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R12" t="s">
+        <v>111</v>
+      </c>
+      <c r="S12" t="s">
+        <v>112</v>
+      </c>
+      <c r="T12" t="s">
         <v>179</v>
       </c>
-      <c r="Q12" t="s">
-        <v>86</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="V12" t="s">
+        <v>85</v>
+      </c>
+      <c r="W12" t="s">
+        <v>111</v>
+      </c>
+      <c r="X12" t="s">
         <v>112</v>
       </c>
-      <c r="S12" t="s">
-        <v>113</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="Y12" t="s">
         <v>180</v>
-      </c>
-      <c r="V12" t="s">
-        <v>86</v>
-      </c>
-      <c r="W12" t="s">
-        <v>112</v>
-      </c>
-      <c r="X12" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
         <v>92</v>
       </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" t="s">
         <v>102</v>
       </c>
-      <c r="I13" t="s">
-        <v>103</v>
-      </c>
       <c r="J13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s">
+        <v>113</v>
+      </c>
+      <c r="N13" t="s">
         <v>114</v>
       </c>
-      <c r="N13" t="s">
-        <v>115</v>
-      </c>
       <c r="O13" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>85</v>
+      </c>
+      <c r="R13" t="s">
+        <v>127</v>
+      </c>
+      <c r="S13" t="s">
+        <v>128</v>
+      </c>
+      <c r="T13" t="s">
         <v>179</v>
       </c>
-      <c r="Q13" t="s">
-        <v>86</v>
-      </c>
-      <c r="R13" t="s">
+      <c r="V13" t="s">
+        <v>85</v>
+      </c>
+      <c r="W13" t="s">
+        <v>127</v>
+      </c>
+      <c r="X13" t="s">
         <v>128</v>
       </c>
-      <c r="S13" t="s">
-        <v>129</v>
-      </c>
-      <c r="T13" t="s">
+      <c r="Y13" t="s">
         <v>180</v>
-      </c>
-      <c r="V13" t="s">
-        <v>86</v>
-      </c>
-      <c r="W13" t="s">
-        <v>128</v>
-      </c>
-      <c r="X13" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s">
         <v>86</v>
       </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>87</v>
       </c>
-      <c r="I14" t="s">
-        <v>88</v>
-      </c>
       <c r="J14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M14" t="s">
+        <v>109</v>
+      </c>
+      <c r="N14" t="s">
         <v>110</v>
       </c>
-      <c r="N14" t="s">
-        <v>111</v>
-      </c>
       <c r="O14" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>85</v>
+      </c>
+      <c r="R14" t="s">
+        <v>154</v>
+      </c>
+      <c r="S14" t="s">
+        <v>155</v>
+      </c>
+      <c r="T14" t="s">
         <v>179</v>
       </c>
-      <c r="Q14" t="s">
-        <v>86</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="V14" t="s">
+        <v>85</v>
+      </c>
+      <c r="W14" t="s">
+        <v>154</v>
+      </c>
+      <c r="X14" t="s">
         <v>155</v>
       </c>
-      <c r="S14" t="s">
-        <v>156</v>
-      </c>
-      <c r="T14" t="s">
+      <c r="Y14" t="s">
         <v>180</v>
-      </c>
-      <c r="V14" t="s">
-        <v>86</v>
-      </c>
-      <c r="W14" t="s">
-        <v>155</v>
-      </c>
-      <c r="X14" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
         <v>96</v>
       </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
       <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
         <v>89</v>
       </c>
-      <c r="G15" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>90</v>
       </c>
-      <c r="I15" t="s">
-        <v>91</v>
-      </c>
       <c r="J15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M15" t="s">
+        <v>172</v>
+      </c>
+      <c r="N15" t="s">
         <v>173</v>
       </c>
-      <c r="N15" t="s">
-        <v>174</v>
-      </c>
       <c r="O15" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>85</v>
+      </c>
+      <c r="R15" t="s">
+        <v>170</v>
+      </c>
+      <c r="S15" t="s">
+        <v>171</v>
+      </c>
+      <c r="T15" t="s">
         <v>179</v>
       </c>
-      <c r="Q15" t="s">
-        <v>86</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="V15" t="s">
+        <v>85</v>
+      </c>
+      <c r="W15" t="s">
+        <v>170</v>
+      </c>
+      <c r="X15" t="s">
         <v>171</v>
       </c>
-      <c r="S15" t="s">
-        <v>172</v>
-      </c>
-      <c r="T15" t="s">
+      <c r="Y15" t="s">
         <v>180</v>
-      </c>
-      <c r="V15" t="s">
-        <v>86</v>
-      </c>
-      <c r="W15" t="s">
-        <v>171</v>
-      </c>
-      <c r="X15" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
         <v>98</v>
       </c>
-      <c r="D16" t="s">
-        <v>99</v>
-      </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" t="s">
         <v>92</v>
       </c>
-      <c r="I16" t="s">
-        <v>93</v>
-      </c>
       <c r="J16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M16" t="s">
+        <v>154</v>
+      </c>
+      <c r="N16" t="s">
         <v>155</v>
       </c>
-      <c r="N16" t="s">
-        <v>156</v>
-      </c>
       <c r="O16" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>85</v>
+      </c>
+      <c r="R16" t="s">
+        <v>97</v>
+      </c>
+      <c r="S16" t="s">
+        <v>98</v>
+      </c>
+      <c r="T16" t="s">
         <v>179</v>
       </c>
-      <c r="Q16" t="s">
-        <v>86</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="V16" t="s">
+        <v>85</v>
+      </c>
+      <c r="W16" t="s">
+        <v>97</v>
+      </c>
+      <c r="X16" t="s">
         <v>98</v>
       </c>
-      <c r="S16" t="s">
-        <v>99</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="Y16" t="s">
         <v>180</v>
-      </c>
-      <c r="V16" t="s">
-        <v>86</v>
-      </c>
-      <c r="W16" t="s">
-        <v>98</v>
-      </c>
-      <c r="X16" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" t="s">
         <v>100</v>
       </c>
-      <c r="D17" t="s">
-        <v>101</v>
-      </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" t="s">
         <v>94</v>
       </c>
-      <c r="I17" t="s">
-        <v>95</v>
-      </c>
       <c r="J17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s">
+        <v>133</v>
+      </c>
+      <c r="N17" t="s">
         <v>134</v>
       </c>
-      <c r="N17" t="s">
-        <v>135</v>
-      </c>
       <c r="O17" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" t="s">
+        <v>109</v>
+      </c>
+      <c r="S17" t="s">
+        <v>110</v>
+      </c>
+      <c r="T17" t="s">
         <v>179</v>
       </c>
-      <c r="Q17" t="s">
-        <v>86</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="V17" t="s">
+        <v>85</v>
+      </c>
+      <c r="W17" t="s">
+        <v>109</v>
+      </c>
+      <c r="X17" t="s">
         <v>110</v>
       </c>
-      <c r="S17" t="s">
-        <v>111</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="Y17" t="s">
         <v>180</v>
-      </c>
-      <c r="V17" t="s">
-        <v>86</v>
-      </c>
-      <c r="W17" t="s">
-        <v>110</v>
-      </c>
-      <c r="X17" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
         <v>102</v>
       </c>
-      <c r="D18" t="s">
-        <v>103</v>
-      </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s">
         <v>96</v>
       </c>
-      <c r="I18" t="s">
-        <v>97</v>
-      </c>
       <c r="J18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M18" t="s">
+        <v>162</v>
+      </c>
+      <c r="N18" t="s">
         <v>163</v>
       </c>
-      <c r="N18" t="s">
-        <v>164</v>
-      </c>
       <c r="O18" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>85</v>
+      </c>
+      <c r="R18" t="s">
+        <v>101</v>
+      </c>
+      <c r="S18" t="s">
+        <v>102</v>
+      </c>
+      <c r="T18" t="s">
         <v>179</v>
       </c>
-      <c r="Q18" t="s">
-        <v>86</v>
-      </c>
-      <c r="R18" t="s">
+      <c r="V18" t="s">
+        <v>85</v>
+      </c>
+      <c r="W18" t="s">
+        <v>101</v>
+      </c>
+      <c r="X18" t="s">
         <v>102</v>
       </c>
-      <c r="S18" t="s">
-        <v>103</v>
-      </c>
-      <c r="T18" t="s">
+      <c r="Y18" t="s">
         <v>180</v>
-      </c>
-      <c r="V18" t="s">
-        <v>86</v>
-      </c>
-      <c r="W18" t="s">
-        <v>102</v>
-      </c>
-      <c r="X18" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" t="s">
+        <v>98</v>
+      </c>
+      <c r="J19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L19" t="s">
+        <v>85</v>
+      </c>
+      <c r="M19" t="s">
+        <v>103</v>
+      </c>
+      <c r="N19" t="s">
+        <v>104</v>
+      </c>
+      <c r="O19" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>85</v>
+      </c>
+      <c r="R19" t="s">
         <v>86</v>
       </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="S19" t="s">
+        <v>87</v>
+      </c>
+      <c r="T19" t="s">
+        <v>179</v>
+      </c>
+      <c r="V19" t="s">
+        <v>85</v>
+      </c>
+      <c r="W19" t="s">
         <v>86</v>
       </c>
-      <c r="H19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" t="s">
-        <v>99</v>
-      </c>
-      <c r="J19" t="s">
-        <v>142</v>
-      </c>
-      <c r="L19" t="s">
-        <v>86</v>
-      </c>
-      <c r="M19" t="s">
-        <v>104</v>
-      </c>
-      <c r="N19" t="s">
-        <v>105</v>
-      </c>
-      <c r="O19" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>86</v>
-      </c>
-      <c r="R19" t="s">
+      <c r="X19" t="s">
         <v>87</v>
       </c>
-      <c r="S19" t="s">
-        <v>88</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="Y19" t="s">
         <v>180</v>
-      </c>
-      <c r="V19" t="s">
-        <v>86</v>
-      </c>
-      <c r="W19" t="s">
-        <v>87</v>
-      </c>
-      <c r="X19" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
         <v>106</v>
       </c>
-      <c r="D20" t="s">
-        <v>107</v>
-      </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" t="s">
         <v>100</v>
       </c>
-      <c r="I20" t="s">
-        <v>101</v>
-      </c>
       <c r="J20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M20" t="s">
+        <v>119</v>
+      </c>
+      <c r="N20" t="s">
         <v>120</v>
       </c>
-      <c r="N20" t="s">
-        <v>121</v>
-      </c>
       <c r="O20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" t="s">
+        <v>113</v>
+      </c>
+      <c r="S20" t="s">
+        <v>114</v>
+      </c>
+      <c r="T20" t="s">
         <v>179</v>
       </c>
-      <c r="Q20" t="s">
-        <v>86</v>
-      </c>
-      <c r="R20" t="s">
+      <c r="V20" t="s">
+        <v>85</v>
+      </c>
+      <c r="W20" t="s">
+        <v>113</v>
+      </c>
+      <c r="X20" t="s">
         <v>114</v>
       </c>
-      <c r="S20" t="s">
-        <v>115</v>
-      </c>
-      <c r="T20" t="s">
+      <c r="Y20" t="s">
         <v>180</v>
-      </c>
-      <c r="V20" t="s">
-        <v>86</v>
-      </c>
-      <c r="W20" t="s">
-        <v>114</v>
-      </c>
-      <c r="X20" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" t="s">
         <v>108</v>
       </c>
-      <c r="D21" t="s">
-        <v>109</v>
-      </c>
       <c r="E21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" t="s">
         <v>104</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
+        <v>141</v>
+      </c>
+      <c r="L21" t="s">
+        <v>85</v>
+      </c>
+      <c r="M21" t="s">
+        <v>164</v>
+      </c>
+      <c r="N21" t="s">
+        <v>165</v>
+      </c>
+      <c r="O21" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>85</v>
+      </c>
+      <c r="R21" t="s">
         <v>105</v>
       </c>
-      <c r="J21" t="s">
-        <v>142</v>
-      </c>
-      <c r="L21" t="s">
-        <v>86</v>
-      </c>
-      <c r="M21" t="s">
-        <v>165</v>
-      </c>
-      <c r="N21" t="s">
-        <v>166</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="S21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T21" t="s">
         <v>179</v>
       </c>
-      <c r="Q21" t="s">
-        <v>86</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="V21" t="s">
+        <v>85</v>
+      </c>
+      <c r="W21" t="s">
+        <v>105</v>
+      </c>
+      <c r="X21" t="s">
         <v>106</v>
       </c>
-      <c r="S21" t="s">
-        <v>107</v>
-      </c>
-      <c r="T21" t="s">
+      <c r="Y21" t="s">
         <v>180</v>
-      </c>
-      <c r="V21" t="s">
-        <v>86</v>
-      </c>
-      <c r="W21" t="s">
-        <v>106</v>
-      </c>
-      <c r="X21" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
         <v>110</v>
       </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
       <c r="E22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" t="s">
         <v>106</v>
       </c>
-      <c r="I22" t="s">
-        <v>107</v>
-      </c>
       <c r="J22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M22" t="s">
+        <v>93</v>
+      </c>
+      <c r="N22" t="s">
         <v>94</v>
       </c>
-      <c r="N22" t="s">
-        <v>95</v>
-      </c>
       <c r="O22" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>85</v>
+      </c>
+      <c r="R22" t="s">
+        <v>131</v>
+      </c>
+      <c r="S22" t="s">
+        <v>132</v>
+      </c>
+      <c r="T22" t="s">
         <v>179</v>
       </c>
-      <c r="Q22" t="s">
-        <v>86</v>
-      </c>
-      <c r="R22" t="s">
+      <c r="V22" t="s">
+        <v>85</v>
+      </c>
+      <c r="W22" t="s">
+        <v>131</v>
+      </c>
+      <c r="X22" t="s">
         <v>132</v>
       </c>
-      <c r="S22" t="s">
-        <v>133</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="Y22" t="s">
         <v>180</v>
-      </c>
-      <c r="V22" t="s">
-        <v>86</v>
-      </c>
-      <c r="W22" t="s">
-        <v>132</v>
-      </c>
-      <c r="X22" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" t="s">
         <v>112</v>
       </c>
-      <c r="D23" t="s">
-        <v>113</v>
-      </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" t="s">
         <v>108</v>
       </c>
-      <c r="I23" t="s">
-        <v>109</v>
-      </c>
       <c r="J23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M23" t="s">
+        <v>174</v>
+      </c>
+      <c r="N23" t="s">
         <v>175</v>
       </c>
-      <c r="N23" t="s">
-        <v>176</v>
-      </c>
       <c r="O23" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>85</v>
+      </c>
+      <c r="R23" t="s">
+        <v>133</v>
+      </c>
+      <c r="S23" t="s">
+        <v>134</v>
+      </c>
+      <c r="T23" t="s">
         <v>179</v>
       </c>
-      <c r="Q23" t="s">
-        <v>86</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="V23" t="s">
+        <v>85</v>
+      </c>
+      <c r="W23" t="s">
+        <v>133</v>
+      </c>
+      <c r="X23" t="s">
         <v>134</v>
       </c>
-      <c r="S23" t="s">
-        <v>135</v>
-      </c>
-      <c r="T23" t="s">
+      <c r="Y23" t="s">
         <v>180</v>
-      </c>
-      <c r="V23" t="s">
-        <v>86</v>
-      </c>
-      <c r="W23" t="s">
-        <v>134</v>
-      </c>
-      <c r="X23" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
         <v>114</v>
       </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
       <c r="E24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s">
+        <v>109</v>
+      </c>
+      <c r="I24" t="s">
         <v>110</v>
       </c>
-      <c r="I24" t="s">
-        <v>111</v>
-      </c>
       <c r="J24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M24" t="s">
+        <v>152</v>
+      </c>
+      <c r="N24" t="s">
         <v>153</v>
       </c>
-      <c r="N24" t="s">
-        <v>154</v>
-      </c>
       <c r="O24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
         <v>116</v>
       </c>
-      <c r="D25" t="s">
-        <v>117</v>
-      </c>
       <c r="E25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" t="s">
         <v>112</v>
       </c>
-      <c r="I25" t="s">
-        <v>113</v>
-      </c>
       <c r="J25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M25" t="s">
+        <v>115</v>
+      </c>
+      <c r="N25" t="s">
         <v>116</v>
       </c>
-      <c r="N25" t="s">
-        <v>117</v>
-      </c>
       <c r="O25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" t="s">
         <v>118</v>
       </c>
-      <c r="D26" t="s">
-        <v>119</v>
-      </c>
       <c r="E26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s">
+        <v>113</v>
+      </c>
+      <c r="I26" t="s">
         <v>114</v>
       </c>
-      <c r="I26" t="s">
-        <v>115</v>
-      </c>
       <c r="J26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M26" t="s">
+        <v>121</v>
+      </c>
+      <c r="N26" t="s">
         <v>122</v>
       </c>
-      <c r="N26" t="s">
-        <v>123</v>
-      </c>
       <c r="O26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" t="s">
         <v>120</v>
       </c>
-      <c r="D27" t="s">
-        <v>121</v>
-      </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" t="s">
         <v>116</v>
       </c>
-      <c r="I27" t="s">
-        <v>117</v>
-      </c>
       <c r="J27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M27" t="s">
+        <v>99</v>
+      </c>
+      <c r="N27" t="s">
         <v>100</v>
       </c>
-      <c r="N27" t="s">
-        <v>101</v>
-      </c>
       <c r="O27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" t="s">
         <v>122</v>
       </c>
-      <c r="D28" t="s">
-        <v>123</v>
-      </c>
       <c r="E28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" t="s">
         <v>118</v>
       </c>
-      <c r="I28" t="s">
-        <v>119</v>
-      </c>
       <c r="J28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M28" t="s">
+        <v>166</v>
+      </c>
+      <c r="N28" t="s">
         <v>167</v>
       </c>
-      <c r="N28" t="s">
-        <v>168</v>
-      </c>
       <c r="O28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" t="s">
         <v>124</v>
       </c>
-      <c r="D29" t="s">
-        <v>125</v>
-      </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s">
+        <v>119</v>
+      </c>
+      <c r="I29" t="s">
         <v>120</v>
       </c>
-      <c r="I29" t="s">
-        <v>121</v>
-      </c>
       <c r="J29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M29" t="s">
+        <v>111</v>
+      </c>
+      <c r="N29" t="s">
         <v>112</v>
       </c>
-      <c r="N29" t="s">
-        <v>113</v>
-      </c>
       <c r="O29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" t="s">
         <v>126</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" t="s">
+        <v>85</v>
+      </c>
+      <c r="H30" t="s">
+        <v>121</v>
+      </c>
+      <c r="I30" t="s">
+        <v>122</v>
+      </c>
+      <c r="J30" t="s">
+        <v>141</v>
+      </c>
+      <c r="L30" t="s">
+        <v>85</v>
+      </c>
+      <c r="M30" t="s">
         <v>127</v>
       </c>
-      <c r="E30" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" t="s">
-        <v>86</v>
-      </c>
-      <c r="H30" t="s">
-        <v>122</v>
-      </c>
-      <c r="I30" t="s">
-        <v>123</v>
-      </c>
-      <c r="J30" t="s">
-        <v>142</v>
-      </c>
-      <c r="L30" t="s">
-        <v>86</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>128</v>
       </c>
-      <c r="N30" t="s">
-        <v>129</v>
-      </c>
       <c r="O30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" t="s">
         <v>128</v>
       </c>
-      <c r="D31" t="s">
-        <v>129</v>
-      </c>
       <c r="E31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s">
+        <v>123</v>
+      </c>
+      <c r="I31" t="s">
         <v>124</v>
       </c>
-      <c r="I31" t="s">
-        <v>125</v>
-      </c>
       <c r="J31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M31" t="s">
+        <v>135</v>
+      </c>
+      <c r="N31" t="s">
         <v>136</v>
       </c>
-      <c r="N31" t="s">
-        <v>137</v>
-      </c>
       <c r="O31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" t="s">
         <v>130</v>
       </c>
-      <c r="D32" t="s">
-        <v>131</v>
-      </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s">
+        <v>125</v>
+      </c>
+      <c r="I32" t="s">
         <v>126</v>
       </c>
-      <c r="I32" t="s">
-        <v>127</v>
-      </c>
       <c r="J32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M32" t="s">
+        <v>160</v>
+      </c>
+      <c r="N32" t="s">
         <v>161</v>
       </c>
-      <c r="N32" t="s">
-        <v>162</v>
-      </c>
       <c r="O32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" t="s">
         <v>132</v>
       </c>
-      <c r="D33" t="s">
-        <v>133</v>
-      </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s">
+        <v>129</v>
+      </c>
+      <c r="I33" t="s">
         <v>130</v>
       </c>
-      <c r="I33" t="s">
-        <v>131</v>
-      </c>
       <c r="J33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M33" t="s">
+        <v>158</v>
+      </c>
+      <c r="N33" t="s">
         <v>159</v>
       </c>
-      <c r="N33" t="s">
-        <v>160</v>
-      </c>
       <c r="O33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" t="s">
         <v>134</v>
       </c>
-      <c r="D34" t="s">
-        <v>135</v>
-      </c>
       <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H34" t="s">
+        <v>131</v>
+      </c>
+      <c r="I34" t="s">
+        <v>132</v>
+      </c>
+      <c r="J34" t="s">
+        <v>141</v>
+      </c>
+      <c r="L34" t="s">
+        <v>85</v>
+      </c>
+      <c r="M34" t="s">
         <v>89</v>
       </c>
-      <c r="G34" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" t="s">
-        <v>132</v>
-      </c>
-      <c r="I34" t="s">
-        <v>133</v>
-      </c>
-      <c r="J34" t="s">
-        <v>142</v>
-      </c>
-      <c r="L34" t="s">
-        <v>86</v>
-      </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>90</v>
       </c>
-      <c r="N34" t="s">
-        <v>91</v>
-      </c>
       <c r="O34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" t="s">
         <v>136</v>
       </c>
-      <c r="D35" t="s">
-        <v>137</v>
-      </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" t="s">
         <v>134</v>
       </c>
-      <c r="I35" t="s">
-        <v>135</v>
-      </c>
       <c r="J35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M35" t="s">
+        <v>146</v>
+      </c>
+      <c r="N35" t="s">
         <v>147</v>
       </c>
-      <c r="N35" t="s">
-        <v>148</v>
-      </c>
       <c r="O35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" t="s">
         <v>138</v>
       </c>
-      <c r="D36" t="s">
-        <v>139</v>
-      </c>
       <c r="E36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s">
+        <v>142</v>
+      </c>
+      <c r="I36" t="s">
         <v>143</v>
       </c>
-      <c r="I36" t="s">
-        <v>144</v>
-      </c>
       <c r="J36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M36" t="s">
+        <v>101</v>
+      </c>
+      <c r="N36" t="s">
         <v>102</v>
       </c>
-      <c r="N36" t="s">
-        <v>103</v>
-      </c>
       <c r="O36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
+        <v>139</v>
+      </c>
+      <c r="D37" t="s">
         <v>140</v>
       </c>
-      <c r="D37" t="s">
-        <v>141</v>
-      </c>
       <c r="E37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s">
+        <v>144</v>
+      </c>
+      <c r="I37" t="s">
         <v>145</v>
       </c>
-      <c r="I37" t="s">
-        <v>146</v>
-      </c>
       <c r="J37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s">
+        <v>156</v>
+      </c>
+      <c r="N37" t="s">
         <v>157</v>
       </c>
-      <c r="N37" t="s">
-        <v>158</v>
-      </c>
       <c r="O37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s">
+        <v>137</v>
+      </c>
+      <c r="I38" t="s">
         <v>138</v>
       </c>
-      <c r="I38" t="s">
-        <v>139</v>
-      </c>
       <c r="J38" t="s">
+        <v>141</v>
+      </c>
+      <c r="L38" t="s">
+        <v>85</v>
+      </c>
+      <c r="M38" t="s">
         <v>142</v>
       </c>
-      <c r="L38" t="s">
-        <v>86</v>
-      </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>143</v>
       </c>
-      <c r="N38" t="s">
-        <v>144</v>
-      </c>
       <c r="O38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s">
+        <v>146</v>
+      </c>
+      <c r="I39" t="s">
         <v>147</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
+        <v>141</v>
+      </c>
+      <c r="L39" t="s">
+        <v>85</v>
+      </c>
+      <c r="M39" t="s">
         <v>148</v>
       </c>
-      <c r="J39" t="s">
-        <v>142</v>
-      </c>
-      <c r="L39" t="s">
-        <v>86</v>
-      </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>149</v>
       </c>
-      <c r="N39" t="s">
-        <v>150</v>
-      </c>
       <c r="O39" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s">
+        <v>148</v>
+      </c>
+      <c r="I40" t="s">
         <v>149</v>
       </c>
-      <c r="I40" t="s">
-        <v>150</v>
-      </c>
       <c r="J40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M40" t="s">
+        <v>137</v>
+      </c>
+      <c r="N40" t="s">
         <v>138</v>
       </c>
-      <c r="N40" t="s">
-        <v>139</v>
-      </c>
       <c r="O40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s">
+        <v>150</v>
+      </c>
+      <c r="I41" t="s">
         <v>151</v>
       </c>
-      <c r="I41" t="s">
-        <v>152</v>
-      </c>
       <c r="J41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M41" t="s">
+        <v>91</v>
+      </c>
+      <c r="N41" t="s">
         <v>92</v>
       </c>
-      <c r="N41" t="s">
-        <v>93</v>
-      </c>
       <c r="O41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s">
+        <v>152</v>
+      </c>
+      <c r="I42" t="s">
         <v>153</v>
       </c>
-      <c r="I42" t="s">
-        <v>154</v>
-      </c>
       <c r="J42" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M42" t="s">
+        <v>97</v>
+      </c>
+      <c r="N42" t="s">
         <v>98</v>
       </c>
-      <c r="N42" t="s">
-        <v>99</v>
-      </c>
       <c r="O42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s">
+        <v>154</v>
+      </c>
+      <c r="I43" t="s">
         <v>155</v>
       </c>
-      <c r="I43" t="s">
-        <v>156</v>
-      </c>
       <c r="J43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M43" t="s">
+        <v>123</v>
+      </c>
+      <c r="N43" t="s">
         <v>124</v>
       </c>
-      <c r="N43" t="s">
-        <v>125</v>
-      </c>
       <c r="O43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s">
+        <v>156</v>
+      </c>
+      <c r="I44" t="s">
         <v>157</v>
       </c>
-      <c r="I44" t="s">
-        <v>158</v>
-      </c>
       <c r="J44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M44" t="s">
+        <v>168</v>
+      </c>
+      <c r="N44" t="s">
         <v>169</v>
       </c>
-      <c r="N44" t="s">
-        <v>170</v>
-      </c>
       <c r="O44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" t="s">
         <v>159</v>
       </c>
-      <c r="I45" t="s">
-        <v>160</v>
-      </c>
       <c r="J45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M45" t="s">
+        <v>125</v>
+      </c>
+      <c r="N45" t="s">
         <v>126</v>
       </c>
-      <c r="N45" t="s">
-        <v>127</v>
-      </c>
       <c r="O45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s">
+        <v>160</v>
+      </c>
+      <c r="I46" t="s">
         <v>161</v>
       </c>
-      <c r="I46" t="s">
-        <v>162</v>
-      </c>
       <c r="J46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M46" t="s">
+        <v>139</v>
+      </c>
+      <c r="N46" t="s">
         <v>140</v>
       </c>
-      <c r="N46" t="s">
-        <v>141</v>
-      </c>
       <c r="O46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s">
+        <v>162</v>
+      </c>
+      <c r="I47" t="s">
         <v>163</v>
       </c>
-      <c r="I47" t="s">
-        <v>164</v>
-      </c>
       <c r="J47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M47" t="s">
+        <v>129</v>
+      </c>
+      <c r="N47" t="s">
         <v>130</v>
       </c>
-      <c r="N47" t="s">
-        <v>131</v>
-      </c>
       <c r="O47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H48" t="s">
+        <v>164</v>
+      </c>
+      <c r="I48" t="s">
         <v>165</v>
       </c>
-      <c r="I48" t="s">
-        <v>166</v>
-      </c>
       <c r="J48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s">
+        <v>117</v>
+      </c>
+      <c r="N48" t="s">
         <v>118</v>
       </c>
-      <c r="N48" t="s">
-        <v>119</v>
-      </c>
       <c r="O48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s">
+        <v>166</v>
+      </c>
+      <c r="I49" t="s">
         <v>167</v>
       </c>
-      <c r="I49" t="s">
-        <v>168</v>
-      </c>
       <c r="J49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M49" t="s">
+        <v>144</v>
+      </c>
+      <c r="N49" t="s">
         <v>145</v>
       </c>
-      <c r="N49" t="s">
-        <v>146</v>
-      </c>
       <c r="O49" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s">
+        <v>139</v>
+      </c>
+      <c r="I50" t="s">
         <v>140</v>
       </c>
-      <c r="I50" t="s">
-        <v>141</v>
-      </c>
       <c r="J50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M50" t="s">
+        <v>131</v>
+      </c>
+      <c r="N50" t="s">
         <v>132</v>
       </c>
-      <c r="N50" t="s">
-        <v>133</v>
-      </c>
       <c r="O50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s">
+        <v>168</v>
+      </c>
+      <c r="I51" t="s">
         <v>169</v>
       </c>
-      <c r="I51" t="s">
-        <v>170</v>
-      </c>
       <c r="J51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M51" t="s">
+        <v>107</v>
+      </c>
+      <c r="N51" t="s">
         <v>108</v>
       </c>
-      <c r="N51" t="s">
-        <v>109</v>
-      </c>
       <c r="O51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G52" t="s">
+        <v>85</v>
+      </c>
+      <c r="H52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I52" t="s">
+        <v>171</v>
+      </c>
+      <c r="J52" t="s">
+        <v>141</v>
+      </c>
+      <c r="L52" t="s">
+        <v>85</v>
+      </c>
+      <c r="M52" t="s">
         <v>86</v>
       </c>
-      <c r="H52" t="s">
-        <v>171</v>
-      </c>
-      <c r="I52" t="s">
-        <v>172</v>
-      </c>
-      <c r="J52" t="s">
-        <v>142</v>
-      </c>
-      <c r="L52" t="s">
-        <v>86</v>
-      </c>
-      <c r="M52" t="s">
+      <c r="N52" t="s">
         <v>87</v>
       </c>
-      <c r="N52" t="s">
-        <v>88</v>
-      </c>
       <c r="O52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s">
+        <v>172</v>
+      </c>
+      <c r="I53" t="s">
         <v>173</v>
       </c>
-      <c r="I53" t="s">
-        <v>174</v>
-      </c>
       <c r="J53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M53" t="s">
+        <v>105</v>
+      </c>
+      <c r="N53" t="s">
         <v>106</v>
       </c>
-      <c r="N53" t="s">
-        <v>107</v>
-      </c>
       <c r="O53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s">
+        <v>174</v>
+      </c>
+      <c r="I54" t="s">
         <v>175</v>
       </c>
-      <c r="I54" t="s">
-        <v>176</v>
-      </c>
       <c r="J54" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M54" t="s">
+        <v>170</v>
+      </c>
+      <c r="N54" t="s">
         <v>171</v>
       </c>
-      <c r="N54" t="s">
-        <v>172</v>
-      </c>
       <c r="O54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M55" t="s">
+        <v>95</v>
+      </c>
+      <c r="N55" t="s">
         <v>96</v>
       </c>
-      <c r="N55" t="s">
-        <v>97</v>
-      </c>
       <c r="O55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2880,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:X58"/>
+  <dimension ref="C4:X57"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
@@ -2907,13 +2904,13 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
         <v>25</v>
       </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="3:24" x14ac:dyDescent="0.45">
@@ -2933,13 +2930,13 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
         <v>27</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="3:24" x14ac:dyDescent="0.45">
@@ -2947,19 +2944,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>8.76</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="3:24" x14ac:dyDescent="0.45">
@@ -2967,19 +2964,19 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
         <v>28</v>
-      </c>
-      <c r="N7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="3:24" x14ac:dyDescent="0.45">
@@ -2987,7 +2984,7 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -3009,13 +3006,13 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10">
         <v>20</v>
       </c>
       <c r="P10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="3:24" x14ac:dyDescent="0.45">
@@ -3023,13 +3020,13 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="1">
         <v>8.76</v>
       </c>
       <c r="P11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q11">
         <v>2023</v>
@@ -3041,12 +3038,12 @@
         <v>2050</v>
       </c>
       <c r="T11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q12" s="2">
         <v>2541</v>
@@ -3058,7 +3055,7 @@
         <v>2541</v>
       </c>
       <c r="T12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="3:24" x14ac:dyDescent="0.45">
@@ -3066,7 +3063,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q13" s="2">
         <v>66</v>
@@ -3078,13 +3075,13 @@
         <v>61</v>
       </c>
       <c r="T13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="3:24" x14ac:dyDescent="0.45">
@@ -3104,7 +3101,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="2">
         <v>4</v>
@@ -3116,13 +3113,13 @@
         <v>4</v>
       </c>
       <c r="T14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="3:24" x14ac:dyDescent="0.45">
@@ -3133,7 +3130,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -3142,7 +3139,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q15" s="2">
         <v>997</v>
@@ -3154,13 +3151,13 @@
         <v>499</v>
       </c>
       <c r="T15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="3:24" x14ac:dyDescent="0.45">
@@ -3168,13 +3165,13 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G16" s="1">
         <v>8.76</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q16" s="2">
         <v>15</v>
@@ -3186,13 +3183,13 @@
         <v>15</v>
       </c>
       <c r="T16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="3:24" x14ac:dyDescent="0.45">
@@ -3200,13 +3197,13 @@
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G17">
         <v>4</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q17" s="2">
         <v>1.5</v>
@@ -3218,7 +3215,7 @@
         <v>1.5</v>
       </c>
       <c r="T17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W17" t="str">
         <f>W13</f>
@@ -3234,13 +3231,13 @@
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q18" s="2">
         <v>3820</v>
@@ -3252,7 +3249,7 @@
         <v>2202</v>
       </c>
       <c r="T18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" ref="W18" si="1">W14</f>
@@ -3268,13 +3265,13 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19">
         <v>30</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q19" s="2">
         <v>113</v>
@@ -3286,7 +3283,7 @@
         <v>94</v>
       </c>
       <c r="T19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" ref="W19" si="2">W15</f>
@@ -3302,13 +3299,13 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q20" s="2">
         <v>3</v>
@@ -3320,7 +3317,7 @@
         <v>3</v>
       </c>
       <c r="T20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" ref="W20" si="3">W16</f>
@@ -3342,7 +3339,7 @@
         <v>0.25</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q21" s="2">
         <v>1477</v>
@@ -3354,7 +3351,7 @@
         <v>1374</v>
       </c>
       <c r="T21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" ref="W21" si="4">W17</f>
@@ -3370,13 +3367,13 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22">
         <v>20</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q22" s="2">
         <v>38</v>
@@ -3388,7 +3385,7 @@
         <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" ref="W22" si="5">W18</f>
@@ -3401,7 +3398,7 @@
     </row>
     <row r="23" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="2">
         <v>1.5</v>
@@ -3413,7 +3410,7 @@
         <v>1.5</v>
       </c>
       <c r="T23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" ref="W23" si="6">W19</f>
@@ -3426,7 +3423,7 @@
     </row>
     <row r="24" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q24" s="2">
         <v>1.5</v>
@@ -3438,7 +3435,7 @@
         <v>1.5</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" ref="T18:T24" si="7">T20</f>
+        <f t="shared" ref="T24" si="7">T20</f>
         <v>E[_]WOF*</v>
       </c>
       <c r="W24" t="str">
@@ -3472,12 +3469,12 @@
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -3488,7 +3485,7 @@
     </row>
     <row r="30" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
@@ -3497,173 +3494,176 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
       <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="1">
-        <v>0.1</v>
+      <c r="G31">
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D32" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G32">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="3:22" x14ac:dyDescent="0.45">
       <c r="D33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G33">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
       <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="C36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" t="s">
-        <v>69</v>
-      </c>
-      <c r="G36" s="1">
+        <v>68</v>
+      </c>
+      <c r="G35" s="1">
         <v>0.9</v>
       </c>
     </row>
-    <row r="39" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C39" t="s">
         <v>20</v>
       </c>
-      <c r="P39" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D39" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" t="s">
+        <v>22</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="S39" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="U39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="V39" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C40" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
         <v>23</v>
       </c>
-      <c r="P40" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="R40" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="S40" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T40" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="U40" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V40" s="6" t="s">
+      <c r="P40" t="s">
         <v>78</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>79</v>
+      </c>
+      <c r="R40" t="s">
+        <v>80</v>
+      </c>
+      <c r="S40">
+        <v>1</v>
+      </c>
+      <c r="T40" t="s">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s">
+        <v>82</v>
+      </c>
+      <c r="V40" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
-      </c>
-      <c r="P41" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>80</v>
-      </c>
-      <c r="R41" t="s">
-        <v>81</v>
-      </c>
-      <c r="S41">
-        <v>1</v>
-      </c>
-      <c r="T41" t="s">
-        <v>82</v>
-      </c>
-      <c r="U41" t="s">
-        <v>83</v>
-      </c>
-      <c r="V41" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="3:22" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C43" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+        <v>23</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C44" t="s">
         <v>40</v>
       </c>
@@ -3671,191 +3671,177 @@
         <v>57</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C45" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" t="s">
-        <v>58</v>
-      </c>
-      <c r="E45" t="s">
-        <v>24</v>
-      </c>
-      <c r="P45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="Q45" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="R45" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S45" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="P46" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q46" t="s">
+      <c r="R44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S44" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="P45" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>79</v>
+      </c>
+      <c r="R45" t="s">
+        <v>83</v>
+      </c>
+      <c r="S45" t="s">
         <v>80</v>
       </c>
-      <c r="R46" t="s">
-        <v>84</v>
-      </c>
-      <c r="S46" t="s">
-        <v>81</v>
+    </row>
+    <row r="47" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="C47" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
+        <v>50</v>
+      </c>
+      <c r="F48" t="s">
+        <v>72</v>
+      </c>
+      <c r="G48" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49">
+        <v>2025</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="3" t="s">
         <v>73</v>
       </c>
       <c r="G49" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D50">
-        <v>2025</v>
+        <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C51" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D51">
-        <v>40</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G51" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.45">
-      <c r="C52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D52">
         <v>2100</v>
       </c>
-      <c r="F52" t="s">
-        <v>76</v>
+      <c r="F51" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C54" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C55" t="s">
-        <v>37</v>
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>2022</v>
+      </c>
+      <c r="J55">
+        <v>2030</v>
+      </c>
+      <c r="K55" t="s">
+        <v>60</v>
+      </c>
+      <c r="L55" t="s">
+        <v>61</v>
+      </c>
+      <c r="M55" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C56" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E56" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F56" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" t="s">
-        <v>51</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I56">
-        <v>2022</v>
-      </c>
-      <c r="J56">
-        <v>2030</v>
-      </c>
-      <c r="K56" t="s">
-        <v>61</v>
+        <v>0.95</v>
       </c>
       <c r="L56" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M56" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
+        <v>67</v>
+      </c>
+      <c r="F57" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57">
+        <v>0.85</v>
+      </c>
+      <c r="L57" t="s">
         <v>64</v>
       </c>
-      <c r="F57" t="s">
-        <v>67</v>
-      </c>
-      <c r="I57">
-        <v>0.95</v>
-      </c>
-      <c r="L57" t="s">
+      <c r="M57" t="s">
         <v>65</v>
-      </c>
-      <c r="M57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.45">
-      <c r="C58" t="s">
-        <v>63</v>
-      </c>
-      <c r="E58" t="s">
-        <v>68</v>
-      </c>
-      <c r="F58" t="s">
-        <v>67</v>
-      </c>
-      <c r="I58">
-        <v>0.85</v>
-      </c>
-      <c r="L58" t="s">
-        <v>65</v>
-      </c>
-      <c r="M58" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33C4BAF-07A6-4AC5-BFB1-016E23C6023C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6B3684-FA35-40C1-BF78-89EDA5740E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="181">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -91,9 +91,6 @@
     <t>PSET_SET</t>
   </si>
   <si>
-    <t>ELE</t>
-  </si>
-  <si>
     <t>EN[_]Hydro*</t>
   </si>
   <si>
@@ -581,6 +578,9 @@
   </si>
   <si>
     <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
+  </si>
+  <si>
+    <t>ELE,CHP,-STG</t>
   </si>
 </sst>
 </file>
@@ -954,20 +954,20 @@
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -975,1875 +975,1875 @@
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" t="s">
-        <v>71</v>
-      </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" t="s">
         <v>70</v>
       </c>
-      <c r="I10" t="s">
-        <v>71</v>
-      </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" t="s">
         <v>70</v>
       </c>
-      <c r="N10" t="s">
-        <v>71</v>
-      </c>
       <c r="O10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S10" t="s">
         <v>70</v>
       </c>
-      <c r="S10" t="s">
-        <v>71</v>
-      </c>
       <c r="T10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W10" t="s">
+        <v>69</v>
+      </c>
+      <c r="X10" t="s">
         <v>70</v>
       </c>
-      <c r="X10" t="s">
-        <v>71</v>
-      </c>
       <c r="Y10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
         <v>85</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>86</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>87</v>
       </c>
-      <c r="E11" t="s">
-        <v>88</v>
-      </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" t="s">
         <v>127</v>
       </c>
-      <c r="I11" t="s">
-        <v>128</v>
-      </c>
       <c r="J11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s">
+        <v>175</v>
+      </c>
+      <c r="N11" t="s">
         <v>176</v>
       </c>
-      <c r="N11" t="s">
-        <v>177</v>
-      </c>
       <c r="O11" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>84</v>
+      </c>
+      <c r="R11" t="s">
+        <v>98</v>
+      </c>
+      <c r="S11" t="s">
+        <v>99</v>
+      </c>
+      <c r="T11" t="s">
         <v>178</v>
       </c>
-      <c r="Q11" t="s">
-        <v>85</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="V11" t="s">
+        <v>84</v>
+      </c>
+      <c r="W11" t="s">
+        <v>98</v>
+      </c>
+      <c r="X11" t="s">
         <v>99</v>
       </c>
-      <c r="S11" t="s">
-        <v>100</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="Y11" t="s">
         <v>179</v>
-      </c>
-      <c r="V11" t="s">
-        <v>85</v>
-      </c>
-      <c r="W11" t="s">
-        <v>99</v>
-      </c>
-      <c r="X11" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" t="s">
         <v>89</v>
       </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s">
+        <v>134</v>
+      </c>
+      <c r="I12" t="s">
         <v>135</v>
       </c>
-      <c r="I12" t="s">
-        <v>136</v>
-      </c>
       <c r="J12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M12" t="s">
+        <v>149</v>
+      </c>
+      <c r="N12" t="s">
         <v>150</v>
       </c>
-      <c r="N12" t="s">
-        <v>151</v>
-      </c>
       <c r="O12" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>84</v>
+      </c>
+      <c r="R12" t="s">
+        <v>110</v>
+      </c>
+      <c r="S12" t="s">
+        <v>111</v>
+      </c>
+      <c r="T12" t="s">
         <v>178</v>
       </c>
-      <c r="Q12" t="s">
-        <v>85</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="V12" t="s">
+        <v>84</v>
+      </c>
+      <c r="W12" t="s">
+        <v>110</v>
+      </c>
+      <c r="X12" t="s">
         <v>111</v>
       </c>
-      <c r="S12" t="s">
-        <v>112</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="Y12" t="s">
         <v>179</v>
-      </c>
-      <c r="V12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W12" t="s">
-        <v>111</v>
-      </c>
-      <c r="X12" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
         <v>91</v>
       </c>
-      <c r="D13" t="s">
-        <v>92</v>
-      </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" t="s">
         <v>101</v>
       </c>
-      <c r="I13" t="s">
-        <v>102</v>
-      </c>
       <c r="J13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M13" t="s">
+        <v>112</v>
+      </c>
+      <c r="N13" t="s">
         <v>113</v>
       </c>
-      <c r="N13" t="s">
-        <v>114</v>
-      </c>
       <c r="O13" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>84</v>
+      </c>
+      <c r="R13" t="s">
+        <v>126</v>
+      </c>
+      <c r="S13" t="s">
+        <v>127</v>
+      </c>
+      <c r="T13" t="s">
         <v>178</v>
       </c>
-      <c r="Q13" t="s">
-        <v>85</v>
-      </c>
-      <c r="R13" t="s">
+      <c r="V13" t="s">
+        <v>84</v>
+      </c>
+      <c r="W13" t="s">
+        <v>126</v>
+      </c>
+      <c r="X13" t="s">
         <v>127</v>
       </c>
-      <c r="S13" t="s">
-        <v>128</v>
-      </c>
-      <c r="T13" t="s">
+      <c r="Y13" t="s">
         <v>179</v>
-      </c>
-      <c r="V13" t="s">
-        <v>85</v>
-      </c>
-      <c r="W13" t="s">
-        <v>127</v>
-      </c>
-      <c r="X13" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" t="s">
         <v>85</v>
       </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>86</v>
       </c>
-      <c r="I14" t="s">
-        <v>87</v>
-      </c>
       <c r="J14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M14" t="s">
+        <v>108</v>
+      </c>
+      <c r="N14" t="s">
         <v>109</v>
       </c>
-      <c r="N14" t="s">
-        <v>110</v>
-      </c>
       <c r="O14" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>84</v>
+      </c>
+      <c r="R14" t="s">
+        <v>153</v>
+      </c>
+      <c r="S14" t="s">
+        <v>154</v>
+      </c>
+      <c r="T14" t="s">
         <v>178</v>
       </c>
-      <c r="Q14" t="s">
-        <v>85</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="V14" t="s">
+        <v>84</v>
+      </c>
+      <c r="W14" t="s">
+        <v>153</v>
+      </c>
+      <c r="X14" t="s">
         <v>154</v>
       </c>
-      <c r="S14" t="s">
-        <v>155</v>
-      </c>
-      <c r="T14" t="s">
+      <c r="Y14" t="s">
         <v>179</v>
-      </c>
-      <c r="V14" t="s">
-        <v>85</v>
-      </c>
-      <c r="W14" t="s">
-        <v>154</v>
-      </c>
-      <c r="X14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
         <v>95</v>
       </c>
-      <c r="D15" t="s">
-        <v>96</v>
-      </c>
       <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" t="s">
         <v>88</v>
       </c>
-      <c r="G15" t="s">
-        <v>85</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>89</v>
       </c>
-      <c r="I15" t="s">
-        <v>90</v>
-      </c>
       <c r="J15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M15" t="s">
+        <v>171</v>
+      </c>
+      <c r="N15" t="s">
         <v>172</v>
       </c>
-      <c r="N15" t="s">
-        <v>173</v>
-      </c>
       <c r="O15" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R15" t="s">
+        <v>169</v>
+      </c>
+      <c r="S15" t="s">
+        <v>170</v>
+      </c>
+      <c r="T15" t="s">
         <v>178</v>
       </c>
-      <c r="Q15" t="s">
-        <v>85</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="V15" t="s">
+        <v>84</v>
+      </c>
+      <c r="W15" t="s">
+        <v>169</v>
+      </c>
+      <c r="X15" t="s">
         <v>170</v>
       </c>
-      <c r="S15" t="s">
-        <v>171</v>
-      </c>
-      <c r="T15" t="s">
+      <c r="Y15" t="s">
         <v>179</v>
-      </c>
-      <c r="V15" t="s">
-        <v>85</v>
-      </c>
-      <c r="W15" t="s">
-        <v>170</v>
-      </c>
-      <c r="X15" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
         <v>97</v>
       </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" t="s">
         <v>91</v>
       </c>
-      <c r="I16" t="s">
-        <v>92</v>
-      </c>
       <c r="J16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M16" t="s">
+        <v>153</v>
+      </c>
+      <c r="N16" t="s">
         <v>154</v>
       </c>
-      <c r="N16" t="s">
-        <v>155</v>
-      </c>
       <c r="O16" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>84</v>
+      </c>
+      <c r="R16" t="s">
+        <v>96</v>
+      </c>
+      <c r="S16" t="s">
+        <v>97</v>
+      </c>
+      <c r="T16" t="s">
         <v>178</v>
       </c>
-      <c r="Q16" t="s">
-        <v>85</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="V16" t="s">
+        <v>84</v>
+      </c>
+      <c r="W16" t="s">
+        <v>96</v>
+      </c>
+      <c r="X16" t="s">
         <v>97</v>
       </c>
-      <c r="S16" t="s">
-        <v>98</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="Y16" t="s">
         <v>179</v>
-      </c>
-      <c r="V16" t="s">
-        <v>85</v>
-      </c>
-      <c r="W16" t="s">
-        <v>97</v>
-      </c>
-      <c r="X16" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
         <v>99</v>
       </c>
-      <c r="D17" t="s">
-        <v>100</v>
-      </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" t="s">
         <v>93</v>
       </c>
-      <c r="I17" t="s">
-        <v>94</v>
-      </c>
       <c r="J17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M17" t="s">
+        <v>132</v>
+      </c>
+      <c r="N17" t="s">
         <v>133</v>
       </c>
-      <c r="N17" t="s">
-        <v>134</v>
-      </c>
       <c r="O17" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>84</v>
+      </c>
+      <c r="R17" t="s">
+        <v>108</v>
+      </c>
+      <c r="S17" t="s">
+        <v>109</v>
+      </c>
+      <c r="T17" t="s">
         <v>178</v>
       </c>
-      <c r="Q17" t="s">
-        <v>85</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="V17" t="s">
+        <v>84</v>
+      </c>
+      <c r="W17" t="s">
+        <v>108</v>
+      </c>
+      <c r="X17" t="s">
         <v>109</v>
       </c>
-      <c r="S17" t="s">
-        <v>110</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="Y17" t="s">
         <v>179</v>
-      </c>
-      <c r="V17" t="s">
-        <v>85</v>
-      </c>
-      <c r="W17" t="s">
-        <v>109</v>
-      </c>
-      <c r="X17" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
         <v>101</v>
       </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" t="s">
         <v>95</v>
       </c>
-      <c r="I18" t="s">
-        <v>96</v>
-      </c>
       <c r="J18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M18" t="s">
+        <v>161</v>
+      </c>
+      <c r="N18" t="s">
         <v>162</v>
       </c>
-      <c r="N18" t="s">
-        <v>163</v>
-      </c>
       <c r="O18" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>84</v>
+      </c>
+      <c r="R18" t="s">
+        <v>100</v>
+      </c>
+      <c r="S18" t="s">
+        <v>101</v>
+      </c>
+      <c r="T18" t="s">
         <v>178</v>
       </c>
-      <c r="Q18" t="s">
-        <v>85</v>
-      </c>
-      <c r="R18" t="s">
+      <c r="V18" t="s">
+        <v>84</v>
+      </c>
+      <c r="W18" t="s">
+        <v>100</v>
+      </c>
+      <c r="X18" t="s">
         <v>101</v>
       </c>
-      <c r="S18" t="s">
-        <v>102</v>
-      </c>
-      <c r="T18" t="s">
+      <c r="Y18" t="s">
         <v>179</v>
-      </c>
-      <c r="V18" t="s">
-        <v>85</v>
-      </c>
-      <c r="W18" t="s">
-        <v>101</v>
-      </c>
-      <c r="X18" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L19" t="s">
+        <v>84</v>
+      </c>
+      <c r="M19" t="s">
+        <v>102</v>
+      </c>
+      <c r="N19" t="s">
+        <v>103</v>
+      </c>
+      <c r="O19" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R19" t="s">
         <v>85</v>
       </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="S19" t="s">
+        <v>86</v>
+      </c>
+      <c r="T19" t="s">
+        <v>178</v>
+      </c>
+      <c r="V19" t="s">
+        <v>84</v>
+      </c>
+      <c r="W19" t="s">
         <v>85</v>
       </c>
-      <c r="H19" t="s">
-        <v>97</v>
-      </c>
-      <c r="I19" t="s">
-        <v>98</v>
-      </c>
-      <c r="J19" t="s">
-        <v>141</v>
-      </c>
-      <c r="L19" t="s">
-        <v>85</v>
-      </c>
-      <c r="M19" t="s">
-        <v>103</v>
-      </c>
-      <c r="N19" t="s">
-        <v>104</v>
-      </c>
-      <c r="O19" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>85</v>
-      </c>
-      <c r="R19" t="s">
+      <c r="X19" t="s">
         <v>86</v>
       </c>
-      <c r="S19" t="s">
-        <v>87</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="Y19" t="s">
         <v>179</v>
-      </c>
-      <c r="V19" t="s">
-        <v>85</v>
-      </c>
-      <c r="W19" t="s">
-        <v>86</v>
-      </c>
-      <c r="X19" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
         <v>105</v>
       </c>
-      <c r="D20" t="s">
-        <v>106</v>
-      </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" t="s">
         <v>99</v>
       </c>
-      <c r="I20" t="s">
-        <v>100</v>
-      </c>
       <c r="J20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M20" t="s">
+        <v>118</v>
+      </c>
+      <c r="N20" t="s">
         <v>119</v>
       </c>
-      <c r="N20" t="s">
-        <v>120</v>
-      </c>
       <c r="O20" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>84</v>
+      </c>
+      <c r="R20" t="s">
+        <v>112</v>
+      </c>
+      <c r="S20" t="s">
+        <v>113</v>
+      </c>
+      <c r="T20" t="s">
         <v>178</v>
       </c>
-      <c r="Q20" t="s">
-        <v>85</v>
-      </c>
-      <c r="R20" t="s">
+      <c r="V20" t="s">
+        <v>84</v>
+      </c>
+      <c r="W20" t="s">
+        <v>112</v>
+      </c>
+      <c r="X20" t="s">
         <v>113</v>
       </c>
-      <c r="S20" t="s">
-        <v>114</v>
-      </c>
-      <c r="T20" t="s">
+      <c r="Y20" t="s">
         <v>179</v>
-      </c>
-      <c r="V20" t="s">
-        <v>85</v>
-      </c>
-      <c r="W20" t="s">
-        <v>113</v>
-      </c>
-      <c r="X20" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
         <v>107</v>
       </c>
-      <c r="D21" t="s">
-        <v>108</v>
-      </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" t="s">
         <v>103</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" t="s">
+        <v>84</v>
+      </c>
+      <c r="M21" t="s">
+        <v>163</v>
+      </c>
+      <c r="N21" t="s">
+        <v>164</v>
+      </c>
+      <c r="O21" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>84</v>
+      </c>
+      <c r="R21" t="s">
         <v>104</v>
       </c>
-      <c r="J21" t="s">
-        <v>141</v>
-      </c>
-      <c r="L21" t="s">
-        <v>85</v>
-      </c>
-      <c r="M21" t="s">
-        <v>164</v>
-      </c>
-      <c r="N21" t="s">
-        <v>165</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="S21" t="s">
+        <v>105</v>
+      </c>
+      <c r="T21" t="s">
         <v>178</v>
       </c>
-      <c r="Q21" t="s">
-        <v>85</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="V21" t="s">
+        <v>84</v>
+      </c>
+      <c r="W21" t="s">
+        <v>104</v>
+      </c>
+      <c r="X21" t="s">
         <v>105</v>
       </c>
-      <c r="S21" t="s">
-        <v>106</v>
-      </c>
-      <c r="T21" t="s">
+      <c r="Y21" t="s">
         <v>179</v>
-      </c>
-      <c r="V21" t="s">
-        <v>85</v>
-      </c>
-      <c r="W21" t="s">
-        <v>105</v>
-      </c>
-      <c r="X21" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
         <v>109</v>
       </c>
-      <c r="D22" t="s">
-        <v>110</v>
-      </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" t="s">
         <v>105</v>
       </c>
-      <c r="I22" t="s">
-        <v>106</v>
-      </c>
       <c r="J22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M22" t="s">
+        <v>92</v>
+      </c>
+      <c r="N22" t="s">
         <v>93</v>
       </c>
-      <c r="N22" t="s">
-        <v>94</v>
-      </c>
       <c r="O22" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>84</v>
+      </c>
+      <c r="R22" t="s">
+        <v>130</v>
+      </c>
+      <c r="S22" t="s">
+        <v>131</v>
+      </c>
+      <c r="T22" t="s">
         <v>178</v>
       </c>
-      <c r="Q22" t="s">
-        <v>85</v>
-      </c>
-      <c r="R22" t="s">
+      <c r="V22" t="s">
+        <v>84</v>
+      </c>
+      <c r="W22" t="s">
+        <v>130</v>
+      </c>
+      <c r="X22" t="s">
         <v>131</v>
       </c>
-      <c r="S22" t="s">
-        <v>132</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="Y22" t="s">
         <v>179</v>
-      </c>
-      <c r="V22" t="s">
-        <v>85</v>
-      </c>
-      <c r="W22" t="s">
-        <v>131</v>
-      </c>
-      <c r="X22" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
         <v>111</v>
       </c>
-      <c r="D23" t="s">
-        <v>112</v>
-      </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
+        <v>106</v>
+      </c>
+      <c r="I23" t="s">
         <v>107</v>
       </c>
-      <c r="I23" t="s">
-        <v>108</v>
-      </c>
       <c r="J23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M23" t="s">
+        <v>173</v>
+      </c>
+      <c r="N23" t="s">
         <v>174</v>
       </c>
-      <c r="N23" t="s">
-        <v>175</v>
-      </c>
       <c r="O23" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>84</v>
+      </c>
+      <c r="R23" t="s">
+        <v>132</v>
+      </c>
+      <c r="S23" t="s">
+        <v>133</v>
+      </c>
+      <c r="T23" t="s">
         <v>178</v>
       </c>
-      <c r="Q23" t="s">
-        <v>85</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="V23" t="s">
+        <v>84</v>
+      </c>
+      <c r="W23" t="s">
+        <v>132</v>
+      </c>
+      <c r="X23" t="s">
         <v>133</v>
       </c>
-      <c r="S23" t="s">
-        <v>134</v>
-      </c>
-      <c r="T23" t="s">
+      <c r="Y23" t="s">
         <v>179</v>
-      </c>
-      <c r="V23" t="s">
-        <v>85</v>
-      </c>
-      <c r="W23" t="s">
-        <v>133</v>
-      </c>
-      <c r="X23" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
         <v>113</v>
       </c>
-      <c r="D24" t="s">
-        <v>114</v>
-      </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" t="s">
         <v>109</v>
       </c>
-      <c r="I24" t="s">
-        <v>110</v>
-      </c>
       <c r="J24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M24" t="s">
+        <v>151</v>
+      </c>
+      <c r="N24" t="s">
         <v>152</v>
       </c>
-      <c r="N24" t="s">
-        <v>153</v>
-      </c>
       <c r="O24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
         <v>115</v>
       </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s">
+        <v>110</v>
+      </c>
+      <c r="I25" t="s">
         <v>111</v>
       </c>
-      <c r="I25" t="s">
-        <v>112</v>
-      </c>
       <c r="J25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M25" t="s">
+        <v>114</v>
+      </c>
+      <c r="N25" t="s">
         <v>115</v>
       </c>
-      <c r="N25" t="s">
-        <v>116</v>
-      </c>
       <c r="O25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
         <v>117</v>
       </c>
-      <c r="D26" t="s">
-        <v>118</v>
-      </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s">
+        <v>112</v>
+      </c>
+      <c r="I26" t="s">
         <v>113</v>
       </c>
-      <c r="I26" t="s">
-        <v>114</v>
-      </c>
       <c r="J26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M26" t="s">
+        <v>120</v>
+      </c>
+      <c r="N26" t="s">
         <v>121</v>
       </c>
-      <c r="N26" t="s">
-        <v>122</v>
-      </c>
       <c r="O26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
         <v>119</v>
       </c>
-      <c r="D27" t="s">
-        <v>120</v>
-      </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s">
+        <v>114</v>
+      </c>
+      <c r="I27" t="s">
         <v>115</v>
       </c>
-      <c r="I27" t="s">
-        <v>116</v>
-      </c>
       <c r="J27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M27" t="s">
+        <v>98</v>
+      </c>
+      <c r="N27" t="s">
         <v>99</v>
       </c>
-      <c r="N27" t="s">
-        <v>100</v>
-      </c>
       <c r="O27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" t="s">
         <v>121</v>
       </c>
-      <c r="D28" t="s">
-        <v>122</v>
-      </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s">
+        <v>116</v>
+      </c>
+      <c r="I28" t="s">
         <v>117</v>
       </c>
-      <c r="I28" t="s">
-        <v>118</v>
-      </c>
       <c r="J28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M28" t="s">
+        <v>165</v>
+      </c>
+      <c r="N28" t="s">
         <v>166</v>
       </c>
-      <c r="N28" t="s">
-        <v>167</v>
-      </c>
       <c r="O28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" t="s">
         <v>123</v>
       </c>
-      <c r="D29" t="s">
-        <v>124</v>
-      </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s">
+        <v>118</v>
+      </c>
+      <c r="I29" t="s">
         <v>119</v>
       </c>
-      <c r="I29" t="s">
-        <v>120</v>
-      </c>
       <c r="J29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M29" t="s">
+        <v>110</v>
+      </c>
+      <c r="N29" t="s">
         <v>111</v>
       </c>
-      <c r="N29" t="s">
-        <v>112</v>
-      </c>
       <c r="O29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" t="s">
         <v>125</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" t="s">
+        <v>120</v>
+      </c>
+      <c r="I30" t="s">
+        <v>121</v>
+      </c>
+      <c r="J30" t="s">
+        <v>140</v>
+      </c>
+      <c r="L30" t="s">
+        <v>84</v>
+      </c>
+      <c r="M30" t="s">
         <v>126</v>
       </c>
-      <c r="E30" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" t="s">
-        <v>85</v>
-      </c>
-      <c r="H30" t="s">
-        <v>121</v>
-      </c>
-      <c r="I30" t="s">
-        <v>122</v>
-      </c>
-      <c r="J30" t="s">
-        <v>141</v>
-      </c>
-      <c r="L30" t="s">
-        <v>85</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>127</v>
       </c>
-      <c r="N30" t="s">
-        <v>128</v>
-      </c>
       <c r="O30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" t="s">
         <v>127</v>
       </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s">
+        <v>122</v>
+      </c>
+      <c r="I31" t="s">
         <v>123</v>
       </c>
-      <c r="I31" t="s">
-        <v>124</v>
-      </c>
       <c r="J31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M31" t="s">
+        <v>134</v>
+      </c>
+      <c r="N31" t="s">
         <v>135</v>
       </c>
-      <c r="N31" t="s">
-        <v>136</v>
-      </c>
       <c r="O31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
         <v>129</v>
       </c>
-      <c r="D32" t="s">
-        <v>130</v>
-      </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s">
+        <v>124</v>
+      </c>
+      <c r="I32" t="s">
         <v>125</v>
       </c>
-      <c r="I32" t="s">
-        <v>126</v>
-      </c>
       <c r="J32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M32" t="s">
+        <v>159</v>
+      </c>
+      <c r="N32" t="s">
         <v>160</v>
       </c>
-      <c r="N32" t="s">
-        <v>161</v>
-      </c>
       <c r="O32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" t="s">
         <v>131</v>
       </c>
-      <c r="D33" t="s">
-        <v>132</v>
-      </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s">
+        <v>128</v>
+      </c>
+      <c r="I33" t="s">
         <v>129</v>
       </c>
-      <c r="I33" t="s">
-        <v>130</v>
-      </c>
       <c r="J33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M33" t="s">
+        <v>157</v>
+      </c>
+      <c r="N33" t="s">
         <v>158</v>
       </c>
-      <c r="N33" t="s">
-        <v>159</v>
-      </c>
       <c r="O33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" t="s">
         <v>133</v>
       </c>
-      <c r="D34" t="s">
-        <v>134</v>
-      </c>
       <c r="E34" t="s">
+        <v>87</v>
+      </c>
+      <c r="G34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I34" t="s">
+        <v>131</v>
+      </c>
+      <c r="J34" t="s">
+        <v>140</v>
+      </c>
+      <c r="L34" t="s">
+        <v>84</v>
+      </c>
+      <c r="M34" t="s">
         <v>88</v>
       </c>
-      <c r="G34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" t="s">
-        <v>131</v>
-      </c>
-      <c r="I34" t="s">
-        <v>132</v>
-      </c>
-      <c r="J34" t="s">
-        <v>141</v>
-      </c>
-      <c r="L34" t="s">
-        <v>85</v>
-      </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>89</v>
       </c>
-      <c r="N34" t="s">
-        <v>90</v>
-      </c>
       <c r="O34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" t="s">
         <v>135</v>
       </c>
-      <c r="D35" t="s">
-        <v>136</v>
-      </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s">
+        <v>132</v>
+      </c>
+      <c r="I35" t="s">
         <v>133</v>
       </c>
-      <c r="I35" t="s">
-        <v>134</v>
-      </c>
       <c r="J35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M35" t="s">
+        <v>145</v>
+      </c>
+      <c r="N35" t="s">
         <v>146</v>
       </c>
-      <c r="N35" t="s">
-        <v>147</v>
-      </c>
       <c r="O35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" t="s">
         <v>137</v>
       </c>
-      <c r="D36" t="s">
-        <v>138</v>
-      </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s">
+        <v>141</v>
+      </c>
+      <c r="I36" t="s">
         <v>142</v>
       </c>
-      <c r="I36" t="s">
-        <v>143</v>
-      </c>
       <c r="J36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M36" t="s">
+        <v>100</v>
+      </c>
+      <c r="N36" t="s">
         <v>101</v>
       </c>
-      <c r="N36" t="s">
-        <v>102</v>
-      </c>
       <c r="O36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" t="s">
         <v>139</v>
       </c>
-      <c r="D37" t="s">
-        <v>140</v>
-      </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I37" t="s">
         <v>144</v>
       </c>
-      <c r="I37" t="s">
-        <v>145</v>
-      </c>
       <c r="J37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M37" t="s">
+        <v>155</v>
+      </c>
+      <c r="N37" t="s">
         <v>156</v>
       </c>
-      <c r="N37" t="s">
-        <v>157</v>
-      </c>
       <c r="O37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s">
+        <v>136</v>
+      </c>
+      <c r="I38" t="s">
         <v>137</v>
       </c>
-      <c r="I38" t="s">
-        <v>138</v>
-      </c>
       <c r="J38" t="s">
+        <v>140</v>
+      </c>
+      <c r="L38" t="s">
+        <v>84</v>
+      </c>
+      <c r="M38" t="s">
         <v>141</v>
       </c>
-      <c r="L38" t="s">
-        <v>85</v>
-      </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>142</v>
       </c>
-      <c r="N38" t="s">
-        <v>143</v>
-      </c>
       <c r="O38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s">
+        <v>145</v>
+      </c>
+      <c r="I39" t="s">
         <v>146</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
+        <v>140</v>
+      </c>
+      <c r="L39" t="s">
+        <v>84</v>
+      </c>
+      <c r="M39" t="s">
         <v>147</v>
       </c>
-      <c r="J39" t="s">
-        <v>141</v>
-      </c>
-      <c r="L39" t="s">
-        <v>85</v>
-      </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>148</v>
       </c>
-      <c r="N39" t="s">
-        <v>149</v>
-      </c>
       <c r="O39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s">
+        <v>147</v>
+      </c>
+      <c r="I40" t="s">
         <v>148</v>
       </c>
-      <c r="I40" t="s">
-        <v>149</v>
-      </c>
       <c r="J40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M40" t="s">
+        <v>136</v>
+      </c>
+      <c r="N40" t="s">
         <v>137</v>
       </c>
-      <c r="N40" t="s">
-        <v>138</v>
-      </c>
       <c r="O40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s">
+        <v>149</v>
+      </c>
+      <c r="I41" t="s">
         <v>150</v>
       </c>
-      <c r="I41" t="s">
-        <v>151</v>
-      </c>
       <c r="J41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M41" t="s">
+        <v>90</v>
+      </c>
+      <c r="N41" t="s">
         <v>91</v>
       </c>
-      <c r="N41" t="s">
-        <v>92</v>
-      </c>
       <c r="O41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s">
+        <v>151</v>
+      </c>
+      <c r="I42" t="s">
         <v>152</v>
       </c>
-      <c r="I42" t="s">
-        <v>153</v>
-      </c>
       <c r="J42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M42" t="s">
+        <v>96</v>
+      </c>
+      <c r="N42" t="s">
         <v>97</v>
       </c>
-      <c r="N42" t="s">
-        <v>98</v>
-      </c>
       <c r="O42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s">
+        <v>153</v>
+      </c>
+      <c r="I43" t="s">
         <v>154</v>
       </c>
-      <c r="I43" t="s">
-        <v>155</v>
-      </c>
       <c r="J43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M43" t="s">
+        <v>122</v>
+      </c>
+      <c r="N43" t="s">
         <v>123</v>
       </c>
-      <c r="N43" t="s">
-        <v>124</v>
-      </c>
       <c r="O43" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s">
+        <v>155</v>
+      </c>
+      <c r="I44" t="s">
         <v>156</v>
       </c>
-      <c r="I44" t="s">
-        <v>157</v>
-      </c>
       <c r="J44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M44" t="s">
+        <v>167</v>
+      </c>
+      <c r="N44" t="s">
         <v>168</v>
       </c>
-      <c r="N44" t="s">
-        <v>169</v>
-      </c>
       <c r="O44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G45" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s">
+        <v>157</v>
+      </c>
+      <c r="I45" t="s">
         <v>158</v>
       </c>
-      <c r="I45" t="s">
-        <v>159</v>
-      </c>
       <c r="J45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L45" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M45" t="s">
+        <v>124</v>
+      </c>
+      <c r="N45" t="s">
         <v>125</v>
       </c>
-      <c r="N45" t="s">
-        <v>126</v>
-      </c>
       <c r="O45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H46" t="s">
+        <v>159</v>
+      </c>
+      <c r="I46" t="s">
         <v>160</v>
       </c>
-      <c r="I46" t="s">
-        <v>161</v>
-      </c>
       <c r="J46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M46" t="s">
+        <v>138</v>
+      </c>
+      <c r="N46" t="s">
         <v>139</v>
       </c>
-      <c r="N46" t="s">
-        <v>140</v>
-      </c>
       <c r="O46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s">
+        <v>161</v>
+      </c>
+      <c r="I47" t="s">
         <v>162</v>
       </c>
-      <c r="I47" t="s">
-        <v>163</v>
-      </c>
       <c r="J47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M47" t="s">
+        <v>128</v>
+      </c>
+      <c r="N47" t="s">
         <v>129</v>
       </c>
-      <c r="N47" t="s">
-        <v>130</v>
-      </c>
       <c r="O47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s">
+        <v>163</v>
+      </c>
+      <c r="I48" t="s">
         <v>164</v>
       </c>
-      <c r="I48" t="s">
-        <v>165</v>
-      </c>
       <c r="J48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M48" t="s">
+        <v>116</v>
+      </c>
+      <c r="N48" t="s">
         <v>117</v>
       </c>
-      <c r="N48" t="s">
-        <v>118</v>
-      </c>
       <c r="O48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s">
+        <v>165</v>
+      </c>
+      <c r="I49" t="s">
         <v>166</v>
       </c>
-      <c r="I49" t="s">
-        <v>167</v>
-      </c>
       <c r="J49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M49" t="s">
+        <v>143</v>
+      </c>
+      <c r="N49" t="s">
         <v>144</v>
       </c>
-      <c r="N49" t="s">
-        <v>145</v>
-      </c>
       <c r="O49" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s">
+        <v>138</v>
+      </c>
+      <c r="I50" t="s">
         <v>139</v>
       </c>
-      <c r="I50" t="s">
-        <v>140</v>
-      </c>
       <c r="J50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M50" t="s">
+        <v>130</v>
+      </c>
+      <c r="N50" t="s">
         <v>131</v>
       </c>
-      <c r="N50" t="s">
-        <v>132</v>
-      </c>
       <c r="O50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s">
+        <v>167</v>
+      </c>
+      <c r="I51" t="s">
         <v>168</v>
       </c>
-      <c r="I51" t="s">
-        <v>169</v>
-      </c>
       <c r="J51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M51" t="s">
+        <v>106</v>
+      </c>
+      <c r="N51" t="s">
         <v>107</v>
       </c>
-      <c r="N51" t="s">
-        <v>108</v>
-      </c>
       <c r="O51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G52" t="s">
+        <v>84</v>
+      </c>
+      <c r="H52" t="s">
+        <v>169</v>
+      </c>
+      <c r="I52" t="s">
+        <v>170</v>
+      </c>
+      <c r="J52" t="s">
+        <v>140</v>
+      </c>
+      <c r="L52" t="s">
+        <v>84</v>
+      </c>
+      <c r="M52" t="s">
         <v>85</v>
       </c>
-      <c r="H52" t="s">
-        <v>170</v>
-      </c>
-      <c r="I52" t="s">
-        <v>171</v>
-      </c>
-      <c r="J52" t="s">
-        <v>141</v>
-      </c>
-      <c r="L52" t="s">
-        <v>85</v>
-      </c>
-      <c r="M52" t="s">
+      <c r="N52" t="s">
         <v>86</v>
       </c>
-      <c r="N52" t="s">
-        <v>87</v>
-      </c>
       <c r="O52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s">
+        <v>171</v>
+      </c>
+      <c r="I53" t="s">
         <v>172</v>
       </c>
-      <c r="I53" t="s">
-        <v>173</v>
-      </c>
       <c r="J53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M53" t="s">
+        <v>104</v>
+      </c>
+      <c r="N53" t="s">
         <v>105</v>
       </c>
-      <c r="N53" t="s">
-        <v>106</v>
-      </c>
       <c r="O53" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G54" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s">
+        <v>173</v>
+      </c>
+      <c r="I54" t="s">
         <v>174</v>
       </c>
-      <c r="I54" t="s">
-        <v>175</v>
-      </c>
       <c r="J54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M54" t="s">
+        <v>169</v>
+      </c>
+      <c r="N54" t="s">
         <v>170</v>
       </c>
-      <c r="N54" t="s">
-        <v>171</v>
-      </c>
       <c r="O54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M55" t="s">
+        <v>94</v>
+      </c>
+      <c r="N55" t="s">
         <v>95</v>
       </c>
-      <c r="N55" t="s">
-        <v>96</v>
-      </c>
       <c r="O55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2877,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:X57"/>
+  <dimension ref="C4:X56"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
@@ -2904,13 +2904,13 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
         <v>24</v>
       </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="3:24" x14ac:dyDescent="0.45">
@@ -2930,13 +2930,13 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" t="s">
         <v>26</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>27</v>
-      </c>
-      <c r="N5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="3:24" x14ac:dyDescent="0.45">
@@ -2944,19 +2944,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>8.76</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
         <v>27</v>
-      </c>
-      <c r="N6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="3:24" x14ac:dyDescent="0.45">
@@ -2964,19 +2964,19 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
         <v>27</v>
-      </c>
-      <c r="N7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="3:24" x14ac:dyDescent="0.45">
@@ -2984,7 +2984,7 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -3006,13 +3006,13 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10">
         <v>20</v>
       </c>
       <c r="P10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="3:24" x14ac:dyDescent="0.45">
@@ -3020,13 +3020,13 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" s="1">
         <v>8.76</v>
       </c>
       <c r="P11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q11">
         <v>2023</v>
@@ -3038,12 +3038,12 @@
         <v>2050</v>
       </c>
       <c r="T11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q12" s="2">
         <v>2541</v>
@@ -3055,7 +3055,7 @@
         <v>2541</v>
       </c>
       <c r="T12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="3:24" x14ac:dyDescent="0.45">
@@ -3063,7 +3063,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q13" s="2">
         <v>66</v>
@@ -3075,13 +3075,13 @@
         <v>61</v>
       </c>
       <c r="T13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="3:24" x14ac:dyDescent="0.45">
@@ -3101,7 +3101,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q14" s="2">
         <v>4</v>
@@ -3113,13 +3113,13 @@
         <v>4</v>
       </c>
       <c r="T14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="3:24" x14ac:dyDescent="0.45">
@@ -3130,7 +3130,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q15" s="2">
         <v>997</v>
@@ -3151,13 +3151,13 @@
         <v>499</v>
       </c>
       <c r="T15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="3:24" x14ac:dyDescent="0.45">
@@ -3165,13 +3165,13 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G16" s="1">
         <v>8.76</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q16" s="2">
         <v>15</v>
@@ -3183,13 +3183,13 @@
         <v>15</v>
       </c>
       <c r="T16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="3:24" x14ac:dyDescent="0.45">
@@ -3197,13 +3197,13 @@
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G17">
         <v>4</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q17" s="2">
         <v>1.5</v>
@@ -3215,7 +3215,7 @@
         <v>1.5</v>
       </c>
       <c r="T17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W17" t="str">
         <f>W13</f>
@@ -3231,13 +3231,13 @@
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q18" s="2">
         <v>3820</v>
@@ -3249,7 +3249,7 @@
         <v>2202</v>
       </c>
       <c r="T18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" ref="W18" si="1">W14</f>
@@ -3265,13 +3265,13 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G19">
         <v>30</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q19" s="2">
         <v>113</v>
@@ -3283,7 +3283,7 @@
         <v>94</v>
       </c>
       <c r="T19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" ref="W19" si="2">W15</f>
@@ -3299,13 +3299,13 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q20" s="2">
         <v>3</v>
@@ -3317,7 +3317,7 @@
         <v>3</v>
       </c>
       <c r="T20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" ref="W20" si="3">W16</f>
@@ -3339,7 +3339,7 @@
         <v>0.25</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q21" s="2">
         <v>1477</v>
@@ -3351,7 +3351,7 @@
         <v>1374</v>
       </c>
       <c r="T21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" ref="W21" si="4">W17</f>
@@ -3367,13 +3367,13 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G22">
         <v>20</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q22" s="2">
         <v>38</v>
@@ -3385,7 +3385,7 @@
         <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" ref="W22" si="5">W18</f>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="23" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q23" s="2">
         <v>1.5</v>
@@ -3410,7 +3410,7 @@
         <v>1.5</v>
       </c>
       <c r="T23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" ref="W23" si="6">W19</f>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="24" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q24" s="2">
         <v>1.5</v>
@@ -3469,12 +3469,12 @@
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -3485,7 +3485,7 @@
     </row>
     <row r="30" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
@@ -3494,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
@@ -3502,7 +3502,7 @@
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G31">
         <v>200</v>
@@ -3513,7 +3513,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G32">
         <v>30</v>
@@ -3524,7 +3524,7 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3532,124 +3532,124 @@
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C34" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="C35" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" t="s">
-        <v>68</v>
-      </c>
-      <c r="G35" s="1">
+        <v>67</v>
+      </c>
+      <c r="G34" s="1">
         <v>0.9</v>
       </c>
     </row>
-    <row r="38" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="P38" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S38" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T38" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V38" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C39" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
         <v>22</v>
       </c>
-      <c r="P39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q39" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R39" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="S39" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="T39" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="U39" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="V39" s="6" t="s">
+      <c r="P39" t="s">
         <v>77</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>78</v>
+      </c>
+      <c r="R39" t="s">
+        <v>79</v>
+      </c>
+      <c r="S39">
+        <v>1</v>
+      </c>
+      <c r="T39" t="s">
+        <v>80</v>
+      </c>
+      <c r="U39" t="s">
+        <v>81</v>
+      </c>
+      <c r="V39" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
-      </c>
-      <c r="P40" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>79</v>
-      </c>
-      <c r="R40" t="s">
-        <v>80</v>
-      </c>
-      <c r="S40">
-        <v>1</v>
-      </c>
-      <c r="T40" t="s">
-        <v>81</v>
-      </c>
-      <c r="U40" t="s">
-        <v>82</v>
-      </c>
-      <c r="V40" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C41" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="3:22" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C42" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C43" t="s">
         <v>39</v>
       </c>
@@ -3657,191 +3657,177 @@
         <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D44" t="s">
-        <v>57</v>
-      </c>
-      <c r="E44" t="s">
-        <v>23</v>
-      </c>
-      <c r="P44" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q43" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="R44" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="S44" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="P45" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q45" t="s">
+      <c r="R43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S43" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="P44" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>78</v>
+      </c>
+      <c r="R44" t="s">
+        <v>82</v>
+      </c>
+      <c r="S44" t="s">
         <v>79</v>
       </c>
-      <c r="R45" t="s">
-        <v>83</v>
-      </c>
-      <c r="S45" t="s">
-        <v>80</v>
+    </row>
+    <row r="46" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="C46" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C47" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" t="s">
+        <v>71</v>
+      </c>
+      <c r="G47" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48">
+        <v>2025</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="3" t="s">
         <v>72</v>
       </c>
       <c r="G48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D49">
-        <v>2025</v>
+        <v>40</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="G49" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D50">
-        <v>40</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G50" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.45">
-      <c r="C51" t="s">
-        <v>48</v>
-      </c>
-      <c r="D51">
         <v>2100</v>
       </c>
-      <c r="F51" t="s">
-        <v>75</v>
+      <c r="F50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C53" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C54" t="s">
-        <v>36</v>
+        <v>23</v>
+      </c>
+      <c r="D54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" t="s">
+        <v>48</v>
+      </c>
+      <c r="F54" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" t="s">
+        <v>49</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>2022</v>
+      </c>
+      <c r="J54">
+        <v>2030</v>
+      </c>
+      <c r="K54" t="s">
+        <v>59</v>
+      </c>
+      <c r="L54" t="s">
+        <v>60</v>
+      </c>
+      <c r="M54" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C55" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E55" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" t="s">
-        <v>50</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I55">
-        <v>2022</v>
-      </c>
-      <c r="J55">
-        <v>2030</v>
-      </c>
-      <c r="K55" t="s">
-        <v>60</v>
+        <v>0.95</v>
       </c>
       <c r="L55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M55" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E56" t="s">
+        <v>66</v>
+      </c>
+      <c r="F56" t="s">
+        <v>65</v>
+      </c>
+      <c r="I56">
+        <v>0.85</v>
+      </c>
+      <c r="L56" t="s">
         <v>63</v>
       </c>
-      <c r="F56" t="s">
-        <v>66</v>
-      </c>
-      <c r="I56">
-        <v>0.95</v>
-      </c>
-      <c r="L56" t="s">
+      <c r="M56" t="s">
         <v>64</v>
-      </c>
-      <c r="M56" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.45">
-      <c r="C57" t="s">
-        <v>62</v>
-      </c>
-      <c r="E57" t="s">
-        <v>67</v>
-      </c>
-      <c r="F57" t="s">
-        <v>66</v>
-      </c>
-      <c r="I57">
-        <v>0.85</v>
-      </c>
-      <c r="L57" t="s">
-        <v>64</v>
-      </c>
-      <c r="M57" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6B3684-FA35-40C1-BF78-89EDA5740E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB22C443-241B-4522-BDEC-C55FBFD53576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="179">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -91,6 +91,9 @@
     <t>PSET_SET</t>
   </si>
   <si>
+    <t>ELE</t>
+  </si>
+  <si>
     <t>EN[_]Hydro*</t>
   </si>
   <si>
@@ -394,10 +397,10 @@
     <t>at grid node - Kalgoorlie_AUS</t>
   </si>
   <si>
-    <t>Dubbo_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Dubbo_AUS</t>
+    <t>MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - MountPiper_AUS</t>
   </si>
   <si>
     <t>TomPriceMine_AUS</t>
@@ -448,12 +451,6 @@
     <t>at grid node - Hazelwood_AUS</t>
   </si>
   <si>
-    <t>MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - MountPiper_AUS</t>
-  </si>
-  <si>
     <t>Bouldercombe_AUS</t>
   </si>
   <si>
@@ -565,22 +562,19 @@
     <t>at grid node - Murray_AUS</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
     <t>BrokenHill_AUS</t>
   </si>
   <si>
     <t>at grid node - BrokenHill_AUS</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
     <t>h_demand</t>
   </si>
   <si>
     <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
-  </si>
-  <si>
-    <t>ELE,CHP,-STG</t>
   </si>
 </sst>
 </file>
@@ -949,25 +943,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:Y55"/>
+  <dimension ref="B3:Y53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -975,1875 +969,1763 @@
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="V9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
         <v>70</v>
       </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" t="s">
-        <v>69</v>
-      </c>
       <c r="I10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" t="s">
         <v>70</v>
       </c>
-      <c r="J10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" t="s">
-        <v>69</v>
-      </c>
       <c r="N10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O10" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" t="s">
         <v>70</v>
       </c>
-      <c r="O10" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>30</v>
-      </c>
-      <c r="R10" t="s">
-        <v>69</v>
-      </c>
       <c r="S10" t="s">
+        <v>71</v>
+      </c>
+      <c r="T10" t="s">
+        <v>20</v>
+      </c>
+      <c r="V10" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10" t="s">
         <v>70</v>
       </c>
-      <c r="T10" t="s">
-        <v>19</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="W10" t="s">
-        <v>69</v>
-      </c>
       <c r="X10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Y10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M11" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="N11" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="O11" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" t="s">
+        <v>99</v>
+      </c>
+      <c r="S11" t="s">
+        <v>100</v>
+      </c>
+      <c r="T11" t="s">
         <v>177</v>
       </c>
-      <c r="Q11" t="s">
-        <v>84</v>
-      </c>
-      <c r="R11" t="s">
-        <v>98</v>
-      </c>
-      <c r="S11" t="s">
+      <c r="V11" t="s">
+        <v>85</v>
+      </c>
+      <c r="W11" t="s">
         <v>99</v>
       </c>
-      <c r="T11" t="s">
+      <c r="X11" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y11" t="s">
         <v>178</v>
-      </c>
-      <c r="V11" t="s">
-        <v>84</v>
-      </c>
-      <c r="W11" t="s">
-        <v>98</v>
-      </c>
-      <c r="X11" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
         <v>88</v>
       </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>87</v>
-      </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M12" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="O12" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R12" t="s">
+        <v>111</v>
+      </c>
+      <c r="S12" t="s">
+        <v>112</v>
+      </c>
+      <c r="T12" t="s">
         <v>177</v>
       </c>
-      <c r="Q12" t="s">
-        <v>84</v>
-      </c>
-      <c r="R12" t="s">
-        <v>110</v>
-      </c>
-      <c r="S12" t="s">
+      <c r="V12" t="s">
+        <v>85</v>
+      </c>
+      <c r="W12" t="s">
         <v>111</v>
       </c>
-      <c r="T12" t="s">
+      <c r="X12" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y12" t="s">
         <v>178</v>
-      </c>
-      <c r="V12" t="s">
-        <v>84</v>
-      </c>
-      <c r="W12" t="s">
-        <v>110</v>
-      </c>
-      <c r="X12" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="N13" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="O13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>85</v>
+      </c>
+      <c r="R13" t="s">
+        <v>127</v>
+      </c>
+      <c r="S13" t="s">
+        <v>128</v>
+      </c>
+      <c r="T13" t="s">
         <v>177</v>
       </c>
-      <c r="Q13" t="s">
-        <v>84</v>
-      </c>
-      <c r="R13" t="s">
-        <v>126</v>
-      </c>
-      <c r="S13" t="s">
+      <c r="V13" t="s">
+        <v>85</v>
+      </c>
+      <c r="W13" t="s">
         <v>127</v>
       </c>
-      <c r="T13" t="s">
+      <c r="X13" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y13" t="s">
         <v>178</v>
-      </c>
-      <c r="V13" t="s">
-        <v>84</v>
-      </c>
-      <c r="W13" t="s">
-        <v>126</v>
-      </c>
-      <c r="X13" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" t="s">
         <v>87</v>
       </c>
-      <c r="G14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>86</v>
-      </c>
       <c r="J14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M14" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="O14" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>85</v>
+      </c>
+      <c r="R14" t="s">
+        <v>152</v>
+      </c>
+      <c r="S14" t="s">
+        <v>153</v>
+      </c>
+      <c r="T14" t="s">
         <v>177</v>
       </c>
-      <c r="Q14" t="s">
-        <v>84</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="V14" t="s">
+        <v>85</v>
+      </c>
+      <c r="W14" t="s">
+        <v>152</v>
+      </c>
+      <c r="X14" t="s">
         <v>153</v>
       </c>
-      <c r="S14" t="s">
-        <v>154</v>
-      </c>
-      <c r="T14" t="s">
+      <c r="Y14" t="s">
         <v>178</v>
-      </c>
-      <c r="V14" t="s">
-        <v>84</v>
-      </c>
-      <c r="W14" t="s">
-        <v>153</v>
-      </c>
-      <c r="X14" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M15" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="N15" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="O15" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>85</v>
+      </c>
+      <c r="R15" t="s">
+        <v>168</v>
+      </c>
+      <c r="S15" t="s">
+        <v>169</v>
+      </c>
+      <c r="T15" t="s">
         <v>177</v>
       </c>
-      <c r="Q15" t="s">
-        <v>84</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="V15" t="s">
+        <v>85</v>
+      </c>
+      <c r="W15" t="s">
+        <v>168</v>
+      </c>
+      <c r="X15" t="s">
         <v>169</v>
       </c>
-      <c r="S15" t="s">
-        <v>170</v>
-      </c>
-      <c r="T15" t="s">
+      <c r="Y15" t="s">
         <v>178</v>
-      </c>
-      <c r="V15" t="s">
-        <v>84</v>
-      </c>
-      <c r="W15" t="s">
-        <v>169</v>
-      </c>
-      <c r="X15" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" t="s">
+        <v>139</v>
+      </c>
+      <c r="L16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M16" t="s">
+        <v>164</v>
+      </c>
+      <c r="N16" t="s">
+        <v>165</v>
+      </c>
+      <c r="O16" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>85</v>
+      </c>
+      <c r="R16" t="s">
         <v>97</v>
       </c>
-      <c r="E16" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" t="s">
-        <v>84</v>
-      </c>
-      <c r="H16" t="s">
-        <v>90</v>
-      </c>
-      <c r="I16" t="s">
-        <v>91</v>
-      </c>
-      <c r="J16" t="s">
-        <v>140</v>
-      </c>
-      <c r="L16" t="s">
-        <v>84</v>
-      </c>
-      <c r="M16" t="s">
-        <v>153</v>
-      </c>
-      <c r="N16" t="s">
-        <v>154</v>
-      </c>
-      <c r="O16" t="s">
+      <c r="S16" t="s">
+        <v>98</v>
+      </c>
+      <c r="T16" t="s">
         <v>177</v>
       </c>
-      <c r="Q16" t="s">
-        <v>84</v>
-      </c>
-      <c r="R16" t="s">
-        <v>96</v>
-      </c>
-      <c r="S16" t="s">
+      <c r="V16" t="s">
+        <v>85</v>
+      </c>
+      <c r="W16" t="s">
         <v>97</v>
       </c>
-      <c r="T16" t="s">
+      <c r="X16" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y16" t="s">
         <v>178</v>
-      </c>
-      <c r="V16" t="s">
-        <v>84</v>
-      </c>
-      <c r="W16" t="s">
-        <v>96</v>
-      </c>
-      <c r="X16" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="N17" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="O17" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" t="s">
+        <v>109</v>
+      </c>
+      <c r="S17" t="s">
+        <v>110</v>
+      </c>
+      <c r="T17" t="s">
         <v>177</v>
       </c>
-      <c r="Q17" t="s">
-        <v>84</v>
-      </c>
-      <c r="R17" t="s">
-        <v>108</v>
-      </c>
-      <c r="S17" t="s">
+      <c r="V17" t="s">
+        <v>85</v>
+      </c>
+      <c r="W17" t="s">
         <v>109</v>
       </c>
-      <c r="T17" t="s">
+      <c r="X17" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y17" t="s">
         <v>178</v>
-      </c>
-      <c r="V17" t="s">
-        <v>84</v>
-      </c>
-      <c r="W17" t="s">
-        <v>108</v>
-      </c>
-      <c r="X17" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s">
+        <v>139</v>
+      </c>
+      <c r="L18" t="s">
+        <v>85</v>
+      </c>
+      <c r="M18" t="s">
+        <v>168</v>
+      </c>
+      <c r="N18" t="s">
+        <v>169</v>
+      </c>
+      <c r="O18" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>85</v>
+      </c>
+      <c r="R18" t="s">
         <v>101</v>
       </c>
-      <c r="E18" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" t="s">
-        <v>94</v>
-      </c>
-      <c r="I18" t="s">
-        <v>95</v>
-      </c>
-      <c r="J18" t="s">
-        <v>140</v>
-      </c>
-      <c r="L18" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18" t="s">
-        <v>161</v>
-      </c>
-      <c r="N18" t="s">
-        <v>162</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="S18" t="s">
+        <v>102</v>
+      </c>
+      <c r="T18" t="s">
         <v>177</v>
       </c>
-      <c r="Q18" t="s">
-        <v>84</v>
-      </c>
-      <c r="R18" t="s">
-        <v>100</v>
-      </c>
-      <c r="S18" t="s">
+      <c r="V18" t="s">
+        <v>85</v>
+      </c>
+      <c r="W18" t="s">
         <v>101</v>
       </c>
-      <c r="T18" t="s">
+      <c r="X18" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y18" t="s">
         <v>178</v>
-      </c>
-      <c r="V18" t="s">
-        <v>84</v>
-      </c>
-      <c r="W18" t="s">
-        <v>100</v>
-      </c>
-      <c r="X18" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" t="s">
+        <v>98</v>
+      </c>
+      <c r="J19" t="s">
+        <v>139</v>
+      </c>
+      <c r="L19" t="s">
+        <v>85</v>
+      </c>
+      <c r="M19" t="s">
+        <v>140</v>
+      </c>
+      <c r="N19" t="s">
+        <v>141</v>
+      </c>
+      <c r="O19" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>85</v>
+      </c>
+      <c r="R19" t="s">
+        <v>86</v>
+      </c>
+      <c r="S19" t="s">
         <v>87</v>
       </c>
-      <c r="G19" t="s">
-        <v>84</v>
-      </c>
-      <c r="H19" t="s">
-        <v>96</v>
-      </c>
-      <c r="I19" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" t="s">
-        <v>140</v>
-      </c>
-      <c r="L19" t="s">
-        <v>84</v>
-      </c>
-      <c r="M19" t="s">
-        <v>102</v>
-      </c>
-      <c r="N19" t="s">
-        <v>103</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="T19" t="s">
         <v>177</v>
       </c>
-      <c r="Q19" t="s">
-        <v>84</v>
-      </c>
-      <c r="R19" t="s">
-        <v>85</v>
-      </c>
-      <c r="S19" t="s">
+      <c r="V19" t="s">
+        <v>85</v>
+      </c>
+      <c r="W19" t="s">
         <v>86</v>
       </c>
-      <c r="T19" t="s">
+      <c r="X19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y19" t="s">
         <v>178</v>
-      </c>
-      <c r="V19" t="s">
-        <v>84</v>
-      </c>
-      <c r="W19" t="s">
-        <v>85</v>
-      </c>
-      <c r="X19" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M20" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="N20" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="O20" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" t="s">
+        <v>113</v>
+      </c>
+      <c r="S20" t="s">
+        <v>114</v>
+      </c>
+      <c r="T20" t="s">
         <v>177</v>
       </c>
-      <c r="Q20" t="s">
-        <v>84</v>
-      </c>
-      <c r="R20" t="s">
-        <v>112</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="V20" t="s">
+        <v>85</v>
+      </c>
+      <c r="W20" t="s">
         <v>113</v>
       </c>
-      <c r="T20" t="s">
+      <c r="X20" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y20" t="s">
         <v>178</v>
-      </c>
-      <c r="V20" t="s">
-        <v>84</v>
-      </c>
-      <c r="W20" t="s">
-        <v>112</v>
-      </c>
-      <c r="X20" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21" t="s">
+        <v>139</v>
+      </c>
+      <c r="L21" t="s">
+        <v>85</v>
+      </c>
+      <c r="M21" t="s">
+        <v>111</v>
+      </c>
+      <c r="N21" t="s">
+        <v>112</v>
+      </c>
+      <c r="O21" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>85</v>
+      </c>
+      <c r="R21" t="s">
+        <v>105</v>
+      </c>
+      <c r="S21" t="s">
         <v>106</v>
       </c>
-      <c r="D21" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" t="s">
-        <v>103</v>
-      </c>
-      <c r="J21" t="s">
-        <v>140</v>
-      </c>
-      <c r="L21" t="s">
-        <v>84</v>
-      </c>
-      <c r="M21" t="s">
-        <v>163</v>
-      </c>
-      <c r="N21" t="s">
-        <v>164</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="T21" t="s">
         <v>177</v>
       </c>
-      <c r="Q21" t="s">
-        <v>84</v>
-      </c>
-      <c r="R21" t="s">
-        <v>104</v>
-      </c>
-      <c r="S21" t="s">
+      <c r="V21" t="s">
+        <v>85</v>
+      </c>
+      <c r="W21" t="s">
         <v>105</v>
       </c>
-      <c r="T21" t="s">
+      <c r="X21" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y21" t="s">
         <v>178</v>
-      </c>
-      <c r="V21" t="s">
-        <v>84</v>
-      </c>
-      <c r="W21" t="s">
-        <v>104</v>
-      </c>
-      <c r="X21" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" t="s">
+        <v>106</v>
+      </c>
+      <c r="J22" t="s">
+        <v>139</v>
+      </c>
+      <c r="L22" t="s">
+        <v>85</v>
+      </c>
+      <c r="M22" t="s">
+        <v>103</v>
+      </c>
+      <c r="N22" t="s">
         <v>104</v>
       </c>
-      <c r="I22" t="s">
-        <v>105</v>
-      </c>
-      <c r="J22" t="s">
-        <v>140</v>
-      </c>
-      <c r="L22" t="s">
-        <v>84</v>
-      </c>
-      <c r="M22" t="s">
-        <v>92</v>
-      </c>
-      <c r="N22" t="s">
-        <v>93</v>
-      </c>
       <c r="O22" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>85</v>
+      </c>
+      <c r="R22" t="s">
+        <v>131</v>
+      </c>
+      <c r="S22" t="s">
+        <v>132</v>
+      </c>
+      <c r="T22" t="s">
         <v>177</v>
       </c>
-      <c r="Q22" t="s">
-        <v>84</v>
-      </c>
-      <c r="R22" t="s">
-        <v>130</v>
-      </c>
-      <c r="S22" t="s">
+      <c r="V22" t="s">
+        <v>85</v>
+      </c>
+      <c r="W22" t="s">
         <v>131</v>
       </c>
-      <c r="T22" t="s">
+      <c r="X22" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y22" t="s">
         <v>178</v>
-      </c>
-      <c r="V22" t="s">
-        <v>84</v>
-      </c>
-      <c r="W22" t="s">
-        <v>130</v>
-      </c>
-      <c r="X22" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M23" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="N23" t="s">
+        <v>138</v>
+      </c>
+      <c r="O23" t="s">
         <v>174</v>
       </c>
-      <c r="O23" t="s">
+      <c r="Q23" t="s">
+        <v>85</v>
+      </c>
+      <c r="R23" t="s">
+        <v>133</v>
+      </c>
+      <c r="S23" t="s">
+        <v>134</v>
+      </c>
+      <c r="T23" t="s">
         <v>177</v>
       </c>
-      <c r="Q23" t="s">
-        <v>84</v>
-      </c>
-      <c r="R23" t="s">
-        <v>132</v>
-      </c>
-      <c r="S23" t="s">
+      <c r="V23" t="s">
+        <v>85</v>
+      </c>
+      <c r="W23" t="s">
         <v>133</v>
       </c>
-      <c r="T23" t="s">
+      <c r="X23" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y23" t="s">
         <v>178</v>
-      </c>
-      <c r="V23" t="s">
-        <v>84</v>
-      </c>
-      <c r="W23" t="s">
-        <v>132</v>
-      </c>
-      <c r="X23" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M24" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="N24" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="O24" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M25" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="N25" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="O25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I26" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" t="s">
+        <v>139</v>
+      </c>
+      <c r="L26" t="s">
+        <v>85</v>
+      </c>
+      <c r="M26" t="s">
         <v>113</v>
       </c>
-      <c r="J26" t="s">
-        <v>140</v>
-      </c>
-      <c r="L26" t="s">
-        <v>84</v>
-      </c>
-      <c r="M26" t="s">
-        <v>120</v>
-      </c>
       <c r="N26" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M27" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="N27" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O27" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M28" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="N28" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="O28" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M29" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="N29" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="O29" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M30" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="N30" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="O30" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M31" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="N31" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="O31" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s">
+        <v>125</v>
+      </c>
+      <c r="I32" t="s">
+        <v>126</v>
+      </c>
+      <c r="J32" t="s">
+        <v>139</v>
+      </c>
+      <c r="L32" t="s">
+        <v>85</v>
+      </c>
+      <c r="M32" t="s">
         <v>129</v>
       </c>
-      <c r="E32" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" t="s">
-        <v>84</v>
-      </c>
-      <c r="H32" t="s">
-        <v>124</v>
-      </c>
-      <c r="I32" t="s">
-        <v>125</v>
-      </c>
-      <c r="J32" t="s">
-        <v>140</v>
-      </c>
-      <c r="L32" t="s">
-        <v>84</v>
-      </c>
-      <c r="M32" t="s">
-        <v>159</v>
-      </c>
       <c r="N32" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="O32" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
+        <v>85</v>
+      </c>
+      <c r="H33" t="s">
+        <v>129</v>
+      </c>
+      <c r="I33" t="s">
         <v>130</v>
       </c>
-      <c r="D33" t="s">
-        <v>131</v>
-      </c>
-      <c r="E33" t="s">
-        <v>87</v>
-      </c>
-      <c r="G33" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" t="s">
-        <v>128</v>
-      </c>
-      <c r="I33" t="s">
-        <v>129</v>
-      </c>
       <c r="J33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O33" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
+        <v>85</v>
+      </c>
+      <c r="H34" t="s">
+        <v>131</v>
+      </c>
+      <c r="I34" t="s">
         <v>132</v>
       </c>
-      <c r="D34" t="s">
-        <v>133</v>
-      </c>
-      <c r="E34" t="s">
-        <v>87</v>
-      </c>
-      <c r="G34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" t="s">
-        <v>130</v>
-      </c>
-      <c r="I34" t="s">
-        <v>131</v>
-      </c>
       <c r="J34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M34" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="N34" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="O34" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" t="s">
         <v>134</v>
       </c>
-      <c r="D35" t="s">
-        <v>135</v>
-      </c>
-      <c r="E35" t="s">
-        <v>87</v>
-      </c>
-      <c r="G35" t="s">
-        <v>84</v>
-      </c>
-      <c r="H35" t="s">
-        <v>132</v>
-      </c>
-      <c r="I35" t="s">
-        <v>133</v>
-      </c>
       <c r="J35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M35" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="N35" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="O35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s">
+        <v>140</v>
+      </c>
+      <c r="I36" t="s">
         <v>141</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
+        <v>139</v>
+      </c>
+      <c r="L36" t="s">
+        <v>85</v>
+      </c>
+      <c r="M36" t="s">
+        <v>99</v>
+      </c>
+      <c r="N36" t="s">
+        <v>100</v>
+      </c>
+      <c r="O36" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="G37" t="s">
+        <v>85</v>
+      </c>
+      <c r="H37" t="s">
         <v>142</v>
       </c>
-      <c r="J36" t="s">
-        <v>140</v>
-      </c>
-      <c r="L36" t="s">
-        <v>84</v>
-      </c>
-      <c r="M36" t="s">
-        <v>100</v>
-      </c>
-      <c r="N36" t="s">
-        <v>101</v>
-      </c>
-      <c r="O36" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" t="s">
-        <v>139</v>
-      </c>
-      <c r="E37" t="s">
-        <v>87</v>
-      </c>
-      <c r="G37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>143</v>
       </c>
-      <c r="I37" t="s">
-        <v>144</v>
-      </c>
       <c r="J37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="N37" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="O37" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I38" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M38" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N38" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="O38" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M39" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="N39" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="O39" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M40" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="N40" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="O40" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M41" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="N41" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="O41" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M42" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="N42" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="O42" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M43" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="N43" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="O43" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s">
+        <v>156</v>
+      </c>
+      <c r="I44" t="s">
+        <v>157</v>
+      </c>
+      <c r="J44" t="s">
+        <v>139</v>
+      </c>
+      <c r="L44" t="s">
+        <v>85</v>
+      </c>
+      <c r="M44" t="s">
+        <v>154</v>
+      </c>
+      <c r="N44" t="s">
         <v>155</v>
       </c>
-      <c r="I44" t="s">
-        <v>156</v>
-      </c>
-      <c r="J44" t="s">
-        <v>140</v>
-      </c>
-      <c r="L44" t="s">
-        <v>84</v>
-      </c>
-      <c r="M44" t="s">
-        <v>167</v>
-      </c>
-      <c r="N44" t="s">
-        <v>168</v>
-      </c>
       <c r="O44" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M45" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="N45" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="O45" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M46" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="N46" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O46" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M47" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="N47" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="O47" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N48" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="O48" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="7:15" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="49" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G49" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="I49" t="s">
+        <v>138</v>
+      </c>
+      <c r="J49" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G50" t="s">
+        <v>85</v>
+      </c>
+      <c r="H50" t="s">
         <v>166</v>
       </c>
-      <c r="J49" t="s">
-        <v>140</v>
-      </c>
-      <c r="L49" t="s">
-        <v>84</v>
-      </c>
-      <c r="M49" t="s">
-        <v>143</v>
-      </c>
-      <c r="N49" t="s">
-        <v>144</v>
-      </c>
-      <c r="O49" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="50" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="G50" t="s">
-        <v>84</v>
-      </c>
-      <c r="H50" t="s">
-        <v>138</v>
-      </c>
       <c r="I50" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="J50" t="s">
-        <v>140</v>
-      </c>
-      <c r="L50" t="s">
-        <v>84</v>
-      </c>
-      <c r="M50" t="s">
-        <v>130</v>
-      </c>
-      <c r="N50" t="s">
-        <v>131</v>
-      </c>
-      <c r="O50" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" spans="7:15" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J51" t="s">
-        <v>140</v>
-      </c>
-      <c r="L51" t="s">
-        <v>84</v>
-      </c>
-      <c r="M51" t="s">
-        <v>106</v>
-      </c>
-      <c r="N51" t="s">
-        <v>107</v>
-      </c>
-      <c r="O51" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="7:15" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J52" t="s">
-        <v>140</v>
-      </c>
-      <c r="L52" t="s">
-        <v>84</v>
-      </c>
-      <c r="M52" t="s">
-        <v>85</v>
-      </c>
-      <c r="N52" t="s">
-        <v>86</v>
-      </c>
-      <c r="O52" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="53" spans="7:15" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="53" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J53" t="s">
-        <v>140</v>
-      </c>
-      <c r="L53" t="s">
-        <v>84</v>
-      </c>
-      <c r="M53" t="s">
-        <v>104</v>
-      </c>
-      <c r="N53" t="s">
-        <v>105</v>
-      </c>
-      <c r="O53" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="54" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="G54" t="s">
-        <v>84</v>
-      </c>
-      <c r="H54" t="s">
-        <v>173</v>
-      </c>
-      <c r="I54" t="s">
-        <v>174</v>
-      </c>
-      <c r="J54" t="s">
-        <v>140</v>
-      </c>
-      <c r="L54" t="s">
-        <v>84</v>
-      </c>
-      <c r="M54" t="s">
-        <v>169</v>
-      </c>
-      <c r="N54" t="s">
-        <v>170</v>
-      </c>
-      <c r="O54" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="55" spans="7:15" x14ac:dyDescent="0.45">
-      <c r="L55" t="s">
-        <v>84</v>
-      </c>
-      <c r="M55" t="s">
-        <v>94</v>
-      </c>
-      <c r="N55" t="s">
-        <v>95</v>
-      </c>
-      <c r="O55" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2877,7 +2759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:X56"/>
+  <dimension ref="C4:X57"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
@@ -2904,13 +2786,13 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="3:24" x14ac:dyDescent="0.45">
@@ -2930,13 +2812,13 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="3:24" x14ac:dyDescent="0.45">
@@ -2944,19 +2826,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>8.76</v>
       </c>
       <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
         <v>28</v>
-      </c>
-      <c r="M6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="3:24" x14ac:dyDescent="0.45">
@@ -2964,19 +2846,19 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="3:24" x14ac:dyDescent="0.45">
@@ -2984,7 +2866,7 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -3006,13 +2888,13 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10">
         <v>20</v>
       </c>
       <c r="P10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="3:24" x14ac:dyDescent="0.45">
@@ -3020,13 +2902,13 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" s="1">
         <v>8.76</v>
       </c>
       <c r="P11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q11">
         <v>2023</v>
@@ -3038,12 +2920,12 @@
         <v>2050</v>
       </c>
       <c r="T11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q12" s="2">
         <v>2541</v>
@@ -3055,7 +2937,7 @@
         <v>2541</v>
       </c>
       <c r="T12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="3:24" x14ac:dyDescent="0.45">
@@ -3063,7 +2945,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q13" s="2">
         <v>66</v>
@@ -3075,13 +2957,13 @@
         <v>61</v>
       </c>
       <c r="T13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="3:24" x14ac:dyDescent="0.45">
@@ -3101,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="2">
         <v>4</v>
@@ -3113,13 +2995,13 @@
         <v>4</v>
       </c>
       <c r="T14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="3:24" x14ac:dyDescent="0.45">
@@ -3130,7 +3012,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -3139,7 +3021,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q15" s="2">
         <v>997</v>
@@ -3151,13 +3033,13 @@
         <v>499</v>
       </c>
       <c r="T15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="3:24" x14ac:dyDescent="0.45">
@@ -3165,13 +3047,13 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" s="1">
         <v>8.76</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q16" s="2">
         <v>15</v>
@@ -3183,13 +3065,13 @@
         <v>15</v>
       </c>
       <c r="T16" t="s">
+        <v>41</v>
+      </c>
+      <c r="W16" t="s">
+        <v>35</v>
+      </c>
+      <c r="X16" t="s">
         <v>40</v>
-      </c>
-      <c r="W16" t="s">
-        <v>34</v>
-      </c>
-      <c r="X16" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="17" spans="3:24" x14ac:dyDescent="0.45">
@@ -3197,13 +3079,13 @@
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17">
         <v>4</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q17" s="2">
         <v>1.5</v>
@@ -3215,7 +3097,7 @@
         <v>1.5</v>
       </c>
       <c r="T17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W17" t="str">
         <f>W13</f>
@@ -3231,13 +3113,13 @@
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q18" s="2">
         <v>3820</v>
@@ -3249,7 +3131,7 @@
         <v>2202</v>
       </c>
       <c r="T18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" ref="W18" si="1">W14</f>
@@ -3265,13 +3147,13 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19">
         <v>30</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q19" s="2">
         <v>113</v>
@@ -3283,7 +3165,7 @@
         <v>94</v>
       </c>
       <c r="T19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" ref="W19" si="2">W15</f>
@@ -3299,13 +3181,13 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q20" s="2">
         <v>3</v>
@@ -3317,7 +3199,7 @@
         <v>3</v>
       </c>
       <c r="T20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" ref="W20" si="3">W16</f>
@@ -3339,7 +3221,7 @@
         <v>0.25</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q21" s="2">
         <v>1477</v>
@@ -3351,7 +3233,7 @@
         <v>1374</v>
       </c>
       <c r="T21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" ref="W21" si="4">W17</f>
@@ -3367,13 +3249,13 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G22">
         <v>20</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q22" s="2">
         <v>38</v>
@@ -3385,7 +3267,7 @@
         <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" ref="W22" si="5">W18</f>
@@ -3398,7 +3280,7 @@
     </row>
     <row r="23" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="2">
         <v>1.5</v>
@@ -3410,7 +3292,7 @@
         <v>1.5</v>
       </c>
       <c r="T23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" ref="W23" si="6">W19</f>
@@ -3423,7 +3305,7 @@
     </row>
     <row r="24" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q24" s="2">
         <v>1.5</v>
@@ -3435,7 +3317,7 @@
         <v>1.5</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" ref="T24" si="7">T20</f>
+        <f t="shared" ref="T18:T24" si="7">T20</f>
         <v>E[_]WOF*</v>
       </c>
       <c r="W24" t="str">
@@ -3469,12 +3351,12 @@
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -3485,7 +3367,7 @@
     </row>
     <row r="30" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
@@ -3494,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
@@ -3502,7 +3384,7 @@
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G31">
         <v>200</v>
@@ -3513,7 +3395,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32">
         <v>30</v>
@@ -3524,7 +3406,7 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3532,124 +3414,124 @@
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C34" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="1">
+        <v>12</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="C35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" t="s">
+        <v>68</v>
+      </c>
+      <c r="G35" s="1">
         <v>0.9</v>
       </c>
     </row>
-    <row r="37" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C37" t="s">
-        <v>18</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="D38" t="s">
+      <c r="P38" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C39" t="s">
         <v>20</v>
       </c>
-      <c r="E38" t="s">
+      <c r="D39" t="s">
         <v>21</v>
-      </c>
-      <c r="P38" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="R38" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="S38" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="T38" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="U38" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="V38" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>44</v>
       </c>
       <c r="E39" t="s">
         <v>22</v>
       </c>
-      <c r="P39" t="s">
+      <c r="P39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="S39" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="U39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="V39" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>78</v>
-      </c>
-      <c r="R39" t="s">
-        <v>79</v>
-      </c>
-      <c r="S39">
-        <v>1</v>
-      </c>
-      <c r="T39" t="s">
-        <v>80</v>
-      </c>
-      <c r="U39" t="s">
-        <v>81</v>
-      </c>
-      <c r="V39" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="40" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="P40" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>79</v>
+      </c>
+      <c r="R40" t="s">
+        <v>80</v>
+      </c>
+      <c r="S40">
+        <v>1</v>
+      </c>
+      <c r="T40" t="s">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s">
+        <v>82</v>
+      </c>
+      <c r="V40" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C41" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C43" t="s">
         <v>39</v>
       </c>
@@ -3657,177 +3539,191 @@
         <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
-      </c>
-      <c r="P43" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+      <c r="P44" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="R43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S43" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="P44" t="s">
+      <c r="Q44" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S44" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="P45" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>79</v>
+      </c>
+      <c r="R45" t="s">
+        <v>83</v>
+      </c>
+      <c r="S45" t="s">
         <v>80</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>78</v>
-      </c>
-      <c r="R44" t="s">
-        <v>82</v>
-      </c>
-      <c r="S44" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="C46" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="47" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C47" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" t="s">
-        <v>49</v>
-      </c>
-      <c r="F47" t="s">
-        <v>71</v>
-      </c>
-      <c r="G47" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
-        <v>47</v>
-      </c>
-      <c r="D48">
-        <v>2025</v>
-      </c>
-      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
         <v>50</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" t="s">
         <v>72</v>
       </c>
       <c r="G48" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49">
+        <v>2025</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" t="s">
         <v>52</v>
-      </c>
-      <c r="D49">
-        <v>40</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G49" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D50">
+        <v>40</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C51" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51">
         <v>2100</v>
       </c>
-      <c r="F50" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.45">
-      <c r="C53" t="s">
-        <v>35</v>
+      <c r="F51" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C54" t="s">
-        <v>23</v>
-      </c>
-      <c r="D54" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54" t="s">
-        <v>48</v>
-      </c>
-      <c r="F54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G54" t="s">
-        <v>49</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>2022</v>
-      </c>
-      <c r="J54">
-        <v>2030</v>
-      </c>
-      <c r="K54" t="s">
-        <v>59</v>
-      </c>
-      <c r="L54" t="s">
-        <v>60</v>
-      </c>
-      <c r="M54" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>2022</v>
+      </c>
+      <c r="J55">
+        <v>2030</v>
+      </c>
+      <c r="K55" t="s">
+        <v>60</v>
+      </c>
+      <c r="L55" t="s">
         <v>61</v>
       </c>
-      <c r="E55" t="s">
-        <v>62</v>
-      </c>
-      <c r="F55" t="s">
-        <v>65</v>
-      </c>
-      <c r="I55">
-        <v>0.95</v>
-      </c>
-      <c r="L55" t="s">
-        <v>63</v>
-      </c>
       <c r="M55" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E56" t="s">
+        <v>63</v>
+      </c>
+      <c r="F56" t="s">
         <v>66</v>
       </c>
-      <c r="F56" t="s">
+      <c r="I56">
+        <v>0.95</v>
+      </c>
+      <c r="L56" t="s">
+        <v>64</v>
+      </c>
+      <c r="M56" t="s">
         <v>65</v>
       </c>
-      <c r="I56">
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C57" t="s">
+        <v>62</v>
+      </c>
+      <c r="E57" t="s">
+        <v>67</v>
+      </c>
+      <c r="F57" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57">
         <v>0.85</v>
       </c>
-      <c r="L56" t="s">
-        <v>63</v>
-      </c>
-      <c r="M56" t="s">
+      <c r="L57" t="s">
         <v>64</v>
+      </c>
+      <c r="M57" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB22C443-241B-4522-BDEC-C55FBFD53576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54B7240-7F13-482E-B1BF-82139A536780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="180">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -575,6 +575,9 @@
   </si>
   <si>
     <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
+  </si>
+  <si>
+    <t>ELE,CHP,-STG</t>
   </si>
 </sst>
 </file>
@@ -3317,7 +3320,7 @@
         <v>1.5</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" ref="T18:T24" si="7">T20</f>
+        <f t="shared" ref="T24" si="7">T20</f>
         <v>E[_]WOF*</v>
       </c>
       <c r="W24" t="str">
@@ -3428,7 +3431,7 @@
     </row>
     <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="D35" t="s">
         <v>68</v>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54B7240-7F13-482E-B1BF-82139A536780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD078CA-9563-4D51-840D-D75302116C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -295,6 +295,9 @@
     <t>~TFM_TOPINS-A</t>
   </si>
   <si>
+    <t>ELE,CHP,-STG</t>
+  </si>
+  <si>
     <t>AUS</t>
   </si>
   <si>
@@ -575,9 +578,6 @@
   </si>
   <si>
     <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
-  </si>
-  <si>
-    <t>ELE,CHP,-STG</t>
   </si>
 </sst>
 </file>
@@ -1051,1684 +1051,1684 @@
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
+        <v>101</v>
+      </c>
+      <c r="T11" t="s">
+        <v>178</v>
+      </c>
+      <c r="V11" t="s">
+        <v>86</v>
+      </c>
+      <c r="W11" t="s">
         <v>100</v>
       </c>
-      <c r="T11" t="s">
-        <v>177</v>
-      </c>
-      <c r="V11" t="s">
-        <v>85</v>
-      </c>
-      <c r="W11" t="s">
-        <v>99</v>
-      </c>
       <c r="X11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
         <v>89</v>
       </c>
-      <c r="D12" t="s">
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" t="s">
+        <v>137</v>
+      </c>
+      <c r="J12" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" t="s">
         <v>90</v>
       </c>
-      <c r="E12" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" t="s">
-        <v>136</v>
-      </c>
-      <c r="J12" t="s">
-        <v>139</v>
-      </c>
-      <c r="L12" t="s">
-        <v>85</v>
-      </c>
-      <c r="M12" t="s">
-        <v>160</v>
-      </c>
       <c r="N12" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="O12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S12" t="s">
+        <v>113</v>
+      </c>
+      <c r="T12" t="s">
+        <v>178</v>
+      </c>
+      <c r="V12" t="s">
+        <v>86</v>
+      </c>
+      <c r="W12" t="s">
         <v>112</v>
       </c>
-      <c r="T12" t="s">
-        <v>177</v>
-      </c>
-      <c r="V12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W12" t="s">
-        <v>111</v>
-      </c>
       <c r="X12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="O13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S13" t="s">
+        <v>129</v>
+      </c>
+      <c r="T13" t="s">
+        <v>178</v>
+      </c>
+      <c r="V13" t="s">
+        <v>86</v>
+      </c>
+      <c r="W13" t="s">
         <v>128</v>
       </c>
-      <c r="T13" t="s">
-        <v>177</v>
-      </c>
-      <c r="V13" t="s">
-        <v>85</v>
-      </c>
-      <c r="W13" t="s">
-        <v>127</v>
-      </c>
       <c r="X13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" t="s">
         <v>88</v>
       </c>
-      <c r="G14" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" t="s">
-        <v>87</v>
-      </c>
       <c r="J14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M14" t="s">
+        <v>104</v>
+      </c>
+      <c r="N14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O14" t="s">
         <v>175</v>
       </c>
-      <c r="N14" t="s">
-        <v>176</v>
-      </c>
-      <c r="O14" t="s">
-        <v>174</v>
-      </c>
       <c r="Q14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S14" t="s">
+        <v>154</v>
+      </c>
+      <c r="T14" t="s">
+        <v>178</v>
+      </c>
+      <c r="V14" t="s">
+        <v>86</v>
+      </c>
+      <c r="W14" t="s">
         <v>153</v>
       </c>
-      <c r="T14" t="s">
-        <v>177</v>
-      </c>
-      <c r="V14" t="s">
-        <v>85</v>
-      </c>
-      <c r="W14" t="s">
-        <v>152</v>
-      </c>
       <c r="X14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N15" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="O15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="S15" t="s">
+        <v>170</v>
+      </c>
+      <c r="T15" t="s">
+        <v>178</v>
+      </c>
+      <c r="V15" t="s">
+        <v>86</v>
+      </c>
+      <c r="W15" t="s">
         <v>169</v>
       </c>
-      <c r="T15" t="s">
-        <v>177</v>
-      </c>
-      <c r="V15" t="s">
-        <v>85</v>
-      </c>
-      <c r="W15" t="s">
-        <v>168</v>
-      </c>
       <c r="X15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M16" t="s">
+        <v>112</v>
+      </c>
+      <c r="N16" t="s">
+        <v>113</v>
+      </c>
+      <c r="O16" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>86</v>
+      </c>
+      <c r="R16" t="s">
         <v>98</v>
       </c>
-      <c r="E16" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" t="s">
-        <v>91</v>
-      </c>
-      <c r="I16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J16" t="s">
-        <v>139</v>
-      </c>
-      <c r="L16" t="s">
-        <v>85</v>
-      </c>
-      <c r="M16" t="s">
-        <v>164</v>
-      </c>
-      <c r="N16" t="s">
-        <v>165</v>
-      </c>
-      <c r="O16" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>85</v>
-      </c>
-      <c r="R16" t="s">
-        <v>97</v>
-      </c>
       <c r="S16" t="s">
+        <v>99</v>
+      </c>
+      <c r="T16" t="s">
+        <v>178</v>
+      </c>
+      <c r="V16" t="s">
+        <v>86</v>
+      </c>
+      <c r="W16" t="s">
         <v>98</v>
       </c>
-      <c r="T16" t="s">
-        <v>177</v>
-      </c>
-      <c r="V16" t="s">
-        <v>85</v>
-      </c>
-      <c r="W16" t="s">
-        <v>97</v>
-      </c>
       <c r="X16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="N17" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="O17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S17" t="s">
+        <v>111</v>
+      </c>
+      <c r="T17" t="s">
+        <v>178</v>
+      </c>
+      <c r="V17" t="s">
+        <v>86</v>
+      </c>
+      <c r="W17" t="s">
         <v>110</v>
       </c>
-      <c r="T17" t="s">
-        <v>177</v>
-      </c>
-      <c r="V17" t="s">
-        <v>85</v>
-      </c>
-      <c r="W17" t="s">
-        <v>109</v>
-      </c>
       <c r="X17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" t="s">
+        <v>86</v>
+      </c>
+      <c r="M18" t="s">
+        <v>141</v>
+      </c>
+      <c r="N18" t="s">
+        <v>142</v>
+      </c>
+      <c r="O18" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>86</v>
+      </c>
+      <c r="R18" t="s">
         <v>102</v>
       </c>
-      <c r="E18" t="s">
-        <v>88</v>
-      </c>
-      <c r="G18" t="s">
-        <v>85</v>
-      </c>
-      <c r="H18" t="s">
-        <v>95</v>
-      </c>
-      <c r="I18" t="s">
-        <v>96</v>
-      </c>
-      <c r="J18" t="s">
-        <v>139</v>
-      </c>
-      <c r="L18" t="s">
-        <v>85</v>
-      </c>
-      <c r="M18" t="s">
-        <v>168</v>
-      </c>
-      <c r="N18" t="s">
-        <v>169</v>
-      </c>
-      <c r="O18" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>85</v>
-      </c>
-      <c r="R18" t="s">
-        <v>101</v>
-      </c>
       <c r="S18" t="s">
+        <v>103</v>
+      </c>
+      <c r="T18" t="s">
+        <v>178</v>
+      </c>
+      <c r="V18" t="s">
+        <v>86</v>
+      </c>
+      <c r="W18" t="s">
         <v>102</v>
       </c>
-      <c r="T18" t="s">
-        <v>177</v>
-      </c>
-      <c r="V18" t="s">
-        <v>85</v>
-      </c>
-      <c r="W18" t="s">
-        <v>101</v>
-      </c>
       <c r="X18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Y18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" t="s">
+        <v>99</v>
+      </c>
+      <c r="J19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L19" t="s">
+        <v>86</v>
+      </c>
+      <c r="M19" t="s">
+        <v>94</v>
+      </c>
+      <c r="N19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O19" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>86</v>
+      </c>
+      <c r="R19" t="s">
+        <v>87</v>
+      </c>
+      <c r="S19" t="s">
         <v>88</v>
       </c>
-      <c r="G19" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" t="s">
-        <v>97</v>
-      </c>
-      <c r="I19" t="s">
-        <v>98</v>
-      </c>
-      <c r="J19" t="s">
-        <v>139</v>
-      </c>
-      <c r="L19" t="s">
-        <v>85</v>
-      </c>
-      <c r="M19" t="s">
-        <v>140</v>
-      </c>
-      <c r="N19" t="s">
-        <v>141</v>
-      </c>
-      <c r="O19" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>85</v>
-      </c>
-      <c r="R19" t="s">
-        <v>86</v>
-      </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
+        <v>178</v>
+      </c>
+      <c r="V19" t="s">
+        <v>86</v>
+      </c>
+      <c r="W19" t="s">
         <v>87</v>
       </c>
-      <c r="T19" t="s">
-        <v>177</v>
-      </c>
-      <c r="V19" t="s">
-        <v>85</v>
-      </c>
-      <c r="W19" t="s">
-        <v>86</v>
-      </c>
       <c r="X19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="N20" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="O20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S20" t="s">
+        <v>115</v>
+      </c>
+      <c r="T20" t="s">
+        <v>178</v>
+      </c>
+      <c r="V20" t="s">
+        <v>86</v>
+      </c>
+      <c r="W20" t="s">
         <v>114</v>
       </c>
-      <c r="T20" t="s">
-        <v>177</v>
-      </c>
-      <c r="V20" t="s">
-        <v>85</v>
-      </c>
-      <c r="W20" t="s">
-        <v>113</v>
-      </c>
       <c r="X20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" t="s">
+        <v>105</v>
+      </c>
+      <c r="J21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" t="s">
+        <v>86</v>
+      </c>
+      <c r="M21" t="s">
+        <v>138</v>
+      </c>
+      <c r="N21" t="s">
+        <v>139</v>
+      </c>
+      <c r="O21" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>86</v>
+      </c>
+      <c r="R21" t="s">
+        <v>106</v>
+      </c>
+      <c r="S21" t="s">
         <v>107</v>
       </c>
-      <c r="D21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" t="s">
-        <v>85</v>
-      </c>
-      <c r="H21" t="s">
-        <v>103</v>
-      </c>
-      <c r="I21" t="s">
-        <v>104</v>
-      </c>
-      <c r="J21" t="s">
-        <v>139</v>
-      </c>
-      <c r="L21" t="s">
-        <v>85</v>
-      </c>
-      <c r="M21" t="s">
-        <v>111</v>
-      </c>
-      <c r="N21" t="s">
-        <v>112</v>
-      </c>
-      <c r="O21" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>85</v>
-      </c>
-      <c r="R21" t="s">
-        <v>105</v>
-      </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
+        <v>178</v>
+      </c>
+      <c r="V21" t="s">
+        <v>86</v>
+      </c>
+      <c r="W21" t="s">
         <v>106</v>
       </c>
-      <c r="T21" t="s">
-        <v>177</v>
-      </c>
-      <c r="V21" t="s">
-        <v>85</v>
-      </c>
-      <c r="W21" t="s">
-        <v>105</v>
-      </c>
       <c r="X21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="N22" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="O22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S22" t="s">
+        <v>133</v>
+      </c>
+      <c r="T22" t="s">
+        <v>178</v>
+      </c>
+      <c r="V22" t="s">
+        <v>86</v>
+      </c>
+      <c r="W22" t="s">
         <v>132</v>
       </c>
-      <c r="T22" t="s">
-        <v>177</v>
-      </c>
-      <c r="V22" t="s">
-        <v>85</v>
-      </c>
-      <c r="W22" t="s">
-        <v>131</v>
-      </c>
       <c r="X22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Y22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" t="s">
+        <v>86</v>
+      </c>
+      <c r="M23" t="s">
+        <v>106</v>
+      </c>
+      <c r="N23" t="s">
         <v>107</v>
       </c>
-      <c r="I23" t="s">
-        <v>108</v>
-      </c>
-      <c r="J23" t="s">
-        <v>139</v>
-      </c>
-      <c r="L23" t="s">
-        <v>85</v>
-      </c>
-      <c r="M23" t="s">
-        <v>137</v>
-      </c>
-      <c r="N23" t="s">
-        <v>138</v>
-      </c>
       <c r="O23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S23" t="s">
+        <v>135</v>
+      </c>
+      <c r="T23" t="s">
+        <v>178</v>
+      </c>
+      <c r="V23" t="s">
+        <v>86</v>
+      </c>
+      <c r="W23" t="s">
         <v>134</v>
       </c>
-      <c r="T23" t="s">
-        <v>177</v>
-      </c>
-      <c r="V23" t="s">
-        <v>85</v>
-      </c>
-      <c r="W23" t="s">
-        <v>133</v>
-      </c>
       <c r="X23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="N25" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="O25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="N26" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="O26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="N27" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="O27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="N28" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="N29" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="O29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="N30" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="O30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="N31" t="s">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="O31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="N32" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="O32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" t="s">
         <v>131</v>
       </c>
-      <c r="D33" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" t="s">
-        <v>85</v>
-      </c>
-      <c r="H33" t="s">
-        <v>129</v>
-      </c>
-      <c r="I33" t="s">
-        <v>130</v>
-      </c>
       <c r="J33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="N33" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="O33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s">
+        <v>132</v>
+      </c>
+      <c r="I34" t="s">
         <v>133</v>
       </c>
-      <c r="D34" t="s">
-        <v>134</v>
-      </c>
-      <c r="E34" t="s">
-        <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" t="s">
-        <v>131</v>
-      </c>
-      <c r="I34" t="s">
-        <v>132</v>
-      </c>
       <c r="J34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="N34" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="O34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
+        <v>86</v>
+      </c>
+      <c r="H35" t="s">
+        <v>134</v>
+      </c>
+      <c r="I35" t="s">
         <v>135</v>
       </c>
-      <c r="D35" t="s">
-        <v>136</v>
-      </c>
-      <c r="E35" t="s">
-        <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" t="s">
-        <v>133</v>
-      </c>
-      <c r="I35" t="s">
-        <v>134</v>
-      </c>
       <c r="J35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="N35" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="O35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="N36" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="O36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I37" t="s">
+        <v>144</v>
+      </c>
+      <c r="J37" t="s">
+        <v>140</v>
+      </c>
+      <c r="L37" t="s">
+        <v>86</v>
+      </c>
+      <c r="M37" t="s">
         <v>143</v>
       </c>
-      <c r="J37" t="s">
-        <v>139</v>
-      </c>
-      <c r="L37" t="s">
-        <v>85</v>
-      </c>
-      <c r="M37" t="s">
-        <v>95</v>
-      </c>
       <c r="N37" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="O37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="N38" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="O38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" t="s">
+        <v>148</v>
+      </c>
+      <c r="J39" t="s">
+        <v>140</v>
+      </c>
+      <c r="L39" t="s">
+        <v>86</v>
+      </c>
+      <c r="M39" t="s">
         <v>147</v>
       </c>
-      <c r="J39" t="s">
-        <v>139</v>
-      </c>
-      <c r="L39" t="s">
-        <v>85</v>
-      </c>
-      <c r="M39" t="s">
-        <v>115</v>
-      </c>
       <c r="N39" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="O39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="N40" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="O40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="N41" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="O41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="N42" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="O42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="N43" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="O43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G44" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L44" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="N44" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="O44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="N45" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="O45" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="N46" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="O46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="N47" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="O47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="N48" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="O48" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G51" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G52" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J52" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G53" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -3320,7 +3320,7 @@
         <v>1.5</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" ref="T24" si="7">T20</f>
+        <f t="shared" ref="T18:T24" si="7">T20</f>
         <v>E[_]WOF*</v>
       </c>
       <c r="W24" t="str">
@@ -3431,7 +3431,7 @@
     </row>
     <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" t="s">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
         <v>68</v>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD078CA-9563-4D51-840D-D75302116C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E32649-FD2B-4C73-92A8-D8B803D96300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1078,10 +1078,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="N11" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="O11" t="s">
         <v>175</v>
@@ -1140,10 +1140,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N12" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="O12" t="s">
         <v>175</v>
@@ -1202,10 +1202,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="N13" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="O13" t="s">
         <v>175</v>
@@ -1264,10 +1264,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="O14" t="s">
         <v>175</v>
@@ -1326,10 +1326,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N15" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="O15" t="s">
         <v>175</v>
@@ -1388,10 +1388,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="N16" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="O16" t="s">
         <v>175</v>
@@ -1450,10 +1450,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="O17" t="s">
         <v>175</v>
@@ -1512,10 +1512,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="N18" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="O18" t="s">
         <v>175</v>
@@ -1574,10 +1574,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="N19" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="O19" t="s">
         <v>175</v>
@@ -1636,10 +1636,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O20" t="s">
         <v>175</v>
@@ -1698,10 +1698,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="N21" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="O21" t="s">
         <v>175</v>
@@ -1760,10 +1760,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="N22" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="O22" t="s">
         <v>175</v>
@@ -1822,10 +1822,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="N23" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="O23" t="s">
         <v>175</v>
@@ -1884,10 +1884,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N24" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="O24" t="s">
         <v>175</v>
@@ -1922,10 +1922,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="N25" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="O25" t="s">
         <v>175</v>
@@ -1960,10 +1960,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="N26" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="O26" t="s">
         <v>175</v>
@@ -1998,10 +1998,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="N27" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="O27" t="s">
         <v>175</v>
@@ -2036,10 +2036,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N28" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="O28" t="s">
         <v>175</v>
@@ -2074,10 +2074,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="N29" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="O29" t="s">
         <v>175</v>
@@ -2112,10 +2112,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="N30" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="O30" t="s">
         <v>175</v>
@@ -2150,10 +2150,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="N31" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="O31" t="s">
         <v>175</v>
@@ -2188,10 +2188,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="N32" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="O32" t="s">
         <v>175</v>
@@ -2226,10 +2226,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="N33" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="O33" t="s">
         <v>175</v>
@@ -2264,10 +2264,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="N34" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="O34" t="s">
         <v>175</v>
@@ -2302,10 +2302,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="N35" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="O35" t="s">
         <v>175</v>
@@ -2340,10 +2340,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="N36" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="O36" t="s">
         <v>175</v>
@@ -2366,10 +2366,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="N37" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="O37" t="s">
         <v>175</v>
@@ -2392,10 +2392,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="N38" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="O38" t="s">
         <v>175</v>
@@ -2418,10 +2418,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N39" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="O39" t="s">
         <v>175</v>
@@ -2444,10 +2444,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="N40" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="O40" t="s">
         <v>175</v>
@@ -2470,10 +2470,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="N41" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="O41" t="s">
         <v>175</v>
@@ -2496,10 +2496,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="N42" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="O42" t="s">
         <v>175</v>
@@ -2522,10 +2522,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="N43" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="O43" t="s">
         <v>175</v>
@@ -2548,10 +2548,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="N44" t="s">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="O44" t="s">
         <v>175</v>
@@ -2574,10 +2574,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="N45" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="O45" t="s">
         <v>175</v>
@@ -2600,10 +2600,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="N46" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="O46" t="s">
         <v>175</v>
@@ -2626,10 +2626,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="N47" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="O47" t="s">
         <v>175</v>
@@ -2652,10 +2652,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="N48" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="O48" t="s">
         <v>175</v>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E32649-FD2B-4C73-92A8-D8B803D96300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE80A242-CF14-42F0-8A8E-E2573E13A152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="184">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -541,6 +541,12 @@
     <t>at grid node - Rowville_AUS</t>
   </si>
   <si>
+    <t>AUS42p8S146p2E_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - AUS42p8S146p2E_AUS</t>
+  </si>
+  <si>
     <t>Merredin_AUS</t>
   </si>
   <si>
@@ -563,6 +569,12 @@
   </si>
   <si>
     <t>at grid node - Murray_AUS</t>
+  </si>
+  <si>
+    <t>OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - OlympicDamWest_AUS</t>
   </si>
   <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
@@ -946,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:Y53"/>
+  <dimension ref="B3:Y54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
@@ -1078,13 +1090,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="N11" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="O11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1096,7 +1108,7 @@
         <v>101</v>
       </c>
       <c r="T11" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V11" t="s">
         <v>86</v>
@@ -1108,7 +1120,7 @@
         <v>101</v>
       </c>
       <c r="Y11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
@@ -1140,13 +1152,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="N12" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="O12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1158,7 +1170,7 @@
         <v>113</v>
       </c>
       <c r="T12" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V12" t="s">
         <v>86</v>
@@ -1170,7 +1182,7 @@
         <v>113</v>
       </c>
       <c r="Y12" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
@@ -1202,13 +1214,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="O13" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1220,7 +1232,7 @@
         <v>129</v>
       </c>
       <c r="T13" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V13" t="s">
         <v>86</v>
@@ -1232,7 +1244,7 @@
         <v>129</v>
       </c>
       <c r="Y13" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
@@ -1264,13 +1276,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>161</v>
+        <v>102</v>
       </c>
       <c r="N14" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="O14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1282,7 +1294,7 @@
         <v>154</v>
       </c>
       <c r="T14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V14" t="s">
         <v>86</v>
@@ -1294,7 +1306,7 @@
         <v>154</v>
       </c>
       <c r="Y14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
@@ -1326,37 +1338,37 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N15" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="O15" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
       </c>
       <c r="R15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="S15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="T15" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V15" t="s">
         <v>86</v>
       </c>
       <c r="W15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="X15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
@@ -1388,13 +1400,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N16" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="O16" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1406,7 +1418,7 @@
         <v>99</v>
       </c>
       <c r="T16" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V16" t="s">
         <v>86</v>
@@ -1418,7 +1430,7 @@
         <v>99</v>
       </c>
       <c r="Y16" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
@@ -1450,13 +1462,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="N17" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="O17" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1468,7 +1480,7 @@
         <v>111</v>
       </c>
       <c r="T17" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V17" t="s">
         <v>86</v>
@@ -1480,7 +1492,7 @@
         <v>111</v>
       </c>
       <c r="Y17" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
@@ -1512,13 +1524,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="N18" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="O18" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1530,7 +1542,7 @@
         <v>103</v>
       </c>
       <c r="T18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V18" t="s">
         <v>86</v>
@@ -1542,7 +1554,7 @@
         <v>103</v>
       </c>
       <c r="Y18" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
@@ -1574,13 +1586,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N19" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O19" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1592,7 +1604,7 @@
         <v>88</v>
       </c>
       <c r="T19" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V19" t="s">
         <v>86</v>
@@ -1604,7 +1616,7 @@
         <v>88</v>
       </c>
       <c r="Y19" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
@@ -1636,13 +1648,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="N20" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="O20" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1654,7 +1666,7 @@
         <v>115</v>
       </c>
       <c r="T20" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V20" t="s">
         <v>86</v>
@@ -1666,7 +1678,7 @@
         <v>115</v>
       </c>
       <c r="Y20" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
@@ -1698,13 +1710,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="N21" t="s">
-        <v>154</v>
+        <v>93</v>
       </c>
       <c r="O21" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1716,7 +1728,7 @@
         <v>107</v>
       </c>
       <c r="T21" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V21" t="s">
         <v>86</v>
@@ -1728,7 +1740,7 @@
         <v>107</v>
       </c>
       <c r="Y21" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
@@ -1760,13 +1772,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="N22" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="O22" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1778,7 +1790,7 @@
         <v>133</v>
       </c>
       <c r="T22" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V22" t="s">
         <v>86</v>
@@ -1790,7 +1802,7 @@
         <v>133</v>
       </c>
       <c r="Y22" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
@@ -1822,13 +1834,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="N23" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="O23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1840,7 +1852,7 @@
         <v>135</v>
       </c>
       <c r="T23" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V23" t="s">
         <v>86</v>
@@ -1852,7 +1864,7 @@
         <v>135</v>
       </c>
       <c r="Y23" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
@@ -1884,13 +1896,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="N24" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="O24" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
@@ -1922,13 +1934,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O25" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
@@ -1960,13 +1972,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="N26" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="O26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
@@ -1998,13 +2010,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="N27" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="O27" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
@@ -2036,13 +2048,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="N28" t="s">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="O28" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
@@ -2074,13 +2086,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="N29" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="O29" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
@@ -2112,13 +2124,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="N30" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="O30" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
@@ -2150,13 +2162,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>96</v>
+        <v>171</v>
       </c>
       <c r="N31" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="O31" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
@@ -2188,13 +2200,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="N32" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="O32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
@@ -2226,13 +2238,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="N33" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="O33" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
@@ -2264,13 +2276,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="N34" t="s">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="O34" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
@@ -2302,13 +2314,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N35" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="O35" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
@@ -2340,13 +2352,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N36" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O36" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
@@ -2366,13 +2378,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="N37" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="O37" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
@@ -2392,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="N38" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="O38" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
@@ -2418,13 +2430,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="N39" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="O39" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
@@ -2444,13 +2456,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="N40" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="O40" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
@@ -2470,13 +2482,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="N41" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="O41" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
@@ -2496,13 +2508,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="N42" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O42" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
@@ -2522,13 +2534,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="N43" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="O43" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
@@ -2548,13 +2560,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="N44" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="O44" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
@@ -2574,13 +2586,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="N45" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="O45" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
@@ -2600,13 +2612,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="N46" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="O46" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
@@ -2626,13 +2638,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="N47" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="O47" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
@@ -2652,16 +2664,16 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="N48" t="s">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="O48" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.45">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G49" t="s">
         <v>86</v>
       </c>
@@ -2674,8 +2686,20 @@
       <c r="J49" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="L49" t="s">
+        <v>86</v>
+      </c>
+      <c r="M49" t="s">
+        <v>114</v>
+      </c>
+      <c r="N49" t="s">
+        <v>115</v>
+      </c>
+      <c r="O49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="50" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G50" t="s">
         <v>86</v>
       </c>
@@ -2688,8 +2712,20 @@
       <c r="J50" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="L50" t="s">
+        <v>86</v>
+      </c>
+      <c r="M50" t="s">
+        <v>134</v>
+      </c>
+      <c r="N50" t="s">
+        <v>135</v>
+      </c>
+      <c r="O50" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G51" t="s">
         <v>86</v>
       </c>
@@ -2703,7 +2739,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="7:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G52" t="s">
         <v>86</v>
       </c>
@@ -2717,7 +2753,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G53" t="s">
         <v>86</v>
       </c>
@@ -2728,6 +2764,20 @@
         <v>174</v>
       </c>
       <c r="J53" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G54" t="s">
+        <v>86</v>
+      </c>
+      <c r="H54" t="s">
+        <v>175</v>
+      </c>
+      <c r="I54" t="s">
+        <v>176</v>
+      </c>
+      <c r="J54" t="s">
         <v>140</v>
       </c>
     </row>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE80A242-CF14-42F0-8A8E-E2573E13A152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70076F4-C73D-4F04-8760-834FF9298B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,10 +541,10 @@
     <t>at grid node - Rowville_AUS</t>
   </si>
   <si>
-    <t>AUS42p8S146p2E_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - AUS42p8S146p2E_AUS</t>
+    <t>Hobart_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Hobart_AUS</t>
   </si>
   <si>
     <t>Merredin_AUS</t>
@@ -571,19 +571,19 @@
     <t>at grid node - Murray_AUS</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - BrokenHill_AUS</t>
+  </si>
+  <si>
     <t>OlympicDamWest_AUS</t>
   </si>
   <si>
     <t>at grid node - OlympicDamWest_AUS</t>
-  </si>
-  <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - BrokenHill_AUS</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1090,13 +1090,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="N11" t="s">
-        <v>178</v>
+        <v>105</v>
       </c>
       <c r="O11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1152,13 +1152,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="N12" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="O12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1214,13 +1214,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="N13" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="O13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1276,13 +1276,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="N14" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="O14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1338,13 +1338,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="N15" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="O15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1400,13 +1400,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="N16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="O16" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1462,13 +1462,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="N17" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="O17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1524,13 +1524,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="N18" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="O18" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1586,13 +1586,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="N19" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="O19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1648,13 +1648,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="N20" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="O20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1710,13 +1710,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="N21" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="O21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1772,13 +1772,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="N22" t="s">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="O22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1834,13 +1834,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N23" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1896,13 +1896,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="N24" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="O24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
@@ -1934,13 +1934,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O25" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
@@ -1972,13 +1972,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="N26" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="O26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
@@ -2010,13 +2010,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="N27" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="O27" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
@@ -2048,13 +2048,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="N28" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="O28" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
@@ -2086,13 +2086,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="N29" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="O29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
@@ -2124,13 +2124,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="N30" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="O30" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
@@ -2168,7 +2168,7 @@
         <v>172</v>
       </c>
       <c r="O31" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
@@ -2200,13 +2200,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N32" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="O32" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
@@ -2238,13 +2238,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="N33" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="O33" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
@@ -2282,7 +2282,7 @@
         <v>168</v>
       </c>
       <c r="O34" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
@@ -2314,13 +2314,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="N35" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="O35" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
@@ -2352,13 +2352,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="N36" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="O36" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
@@ -2378,13 +2378,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N37" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="O37" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
@@ -2404,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="N38" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="O38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
@@ -2430,13 +2430,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="N39" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="O39" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
@@ -2456,13 +2456,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="N40" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
@@ -2482,13 +2482,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="N41" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="O41" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
@@ -2508,13 +2508,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O42" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
@@ -2534,13 +2534,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="N43" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="O43" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
@@ -2560,13 +2560,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="N44" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="O44" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
@@ -2586,13 +2586,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="N45" t="s">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="O45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
@@ -2612,13 +2612,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="N46" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="O46" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
@@ -2638,13 +2638,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="N47" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="O47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
@@ -2664,13 +2664,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="N48" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="O48" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -2690,13 +2690,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="N49" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O49" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -2716,13 +2716,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="N50" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="O50" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70076F4-C73D-4F04-8760-834FF9298B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C908AC4-FCEB-4834-85E0-8FD14DF5955A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,10 +376,10 @@
     <t>at grid node - SouthMorang_AUS</t>
   </si>
   <si>
-    <t>Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Brisbane_AUS</t>
+    <t>Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Ipswich_AUS</t>
   </si>
   <si>
     <t>SydneyWest_AUS</t>
@@ -541,10 +541,10 @@
     <t>at grid node - Rowville_AUS</t>
   </si>
   <si>
-    <t>Hobart_AUS</t>
-  </si>
-  <si>
-    <t>at grid node - Hobart_AUS</t>
+    <t>Kingston_AUS</t>
+  </si>
+  <si>
+    <t>at grid node - Kingston_AUS</t>
   </si>
   <si>
     <t>Merredin_AUS</t>
@@ -1090,10 +1090,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O11" t="s">
         <v>177</v>
@@ -1152,10 +1152,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
         <v>177</v>
@@ -1214,10 +1214,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="N13" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="O13" t="s">
         <v>177</v>
@@ -1276,10 +1276,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="N14" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="O14" t="s">
         <v>177</v>
@@ -1338,10 +1338,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="N15" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="O15" t="s">
         <v>177</v>
@@ -1400,10 +1400,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="N16" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="O16" t="s">
         <v>177</v>
@@ -1462,10 +1462,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="N17" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="O17" t="s">
         <v>177</v>
@@ -1524,10 +1524,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="N18" t="s">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="O18" t="s">
         <v>177</v>
@@ -1586,10 +1586,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="N19" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="O19" t="s">
         <v>177</v>
@@ -1648,10 +1648,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="N20" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="O20" t="s">
         <v>177</v>
@@ -1710,10 +1710,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="N21" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="O21" t="s">
         <v>177</v>
@@ -1772,10 +1772,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O22" t="s">
         <v>177</v>
@@ -1834,10 +1834,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O23" t="s">
         <v>177</v>
@@ -1896,10 +1896,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="N24" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="O24" t="s">
         <v>177</v>
@@ -1934,10 +1934,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="N25" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="O25" t="s">
         <v>177</v>
@@ -1972,10 +1972,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="N26" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="O26" t="s">
         <v>177</v>
@@ -2010,10 +2010,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="N27" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="O27" t="s">
         <v>177</v>
@@ -2048,10 +2048,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="N28" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="O28" t="s">
         <v>177</v>
@@ -2086,10 +2086,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="N29" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
         <v>177</v>
@@ -2124,10 +2124,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="N30" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="O30" t="s">
         <v>177</v>
@@ -2162,10 +2162,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="N31" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="O31" t="s">
         <v>177</v>
@@ -2200,10 +2200,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="N32" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="O32" t="s">
         <v>177</v>
@@ -2238,10 +2238,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="N33" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="O33" t="s">
         <v>177</v>
@@ -2276,10 +2276,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="N34" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="O34" t="s">
         <v>177</v>
@@ -2314,10 +2314,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="N35" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="O35" t="s">
         <v>177</v>
@@ -2352,10 +2352,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N36" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O36" t="s">
         <v>177</v>
@@ -2378,10 +2378,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="N37" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="O37" t="s">
         <v>177</v>
@@ -2404,10 +2404,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="N38" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="O38" t="s">
         <v>177</v>
@@ -2456,10 +2456,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="N40" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="O40" t="s">
         <v>177</v>
@@ -2482,10 +2482,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="N41" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="O41" t="s">
         <v>177</v>
@@ -2508,10 +2508,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="N42" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="O42" t="s">
         <v>177</v>
@@ -2534,10 +2534,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="N43" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="O43" t="s">
         <v>177</v>
@@ -2560,10 +2560,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="N44" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="O44" t="s">
         <v>177</v>
@@ -2586,10 +2586,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="N45" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="O45" t="s">
         <v>177</v>
@@ -2612,10 +2612,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N46" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="O46" t="s">
         <v>177</v>
@@ -2638,10 +2638,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="N47" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="O47" t="s">
         <v>177</v>
@@ -2664,10 +2664,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="N48" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="O48" t="s">
         <v>177</v>
@@ -2690,10 +2690,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="N49" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="O49" t="s">
         <v>177</v>
@@ -2716,10 +2716,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="N50" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="O50" t="s">
         <v>177</v>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C908AC4-FCEB-4834-85E0-8FD14DF5955A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBA37CB-CE5C-4D5E-BB66-803B0E2BBE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1090,10 +1090,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="O11" t="s">
         <v>177</v>
@@ -1152,10 +1152,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="N12" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="O12" t="s">
         <v>177</v>
@@ -1214,10 +1214,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="N13" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="O13" t="s">
         <v>177</v>
@@ -1276,10 +1276,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="O14" t="s">
         <v>177</v>
@@ -1338,10 +1338,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="N15" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="O15" t="s">
         <v>177</v>
@@ -1400,10 +1400,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="N16" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="O16" t="s">
         <v>177</v>
@@ -1462,10 +1462,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="N17" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="O17" t="s">
         <v>177</v>
@@ -1524,10 +1524,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="N18" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="O18" t="s">
         <v>177</v>
@@ -1586,10 +1586,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="N19" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="O19" t="s">
         <v>177</v>
@@ -1648,10 +1648,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="N20" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="O20" t="s">
         <v>177</v>
@@ -1710,10 +1710,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="N21" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="O21" t="s">
         <v>177</v>
@@ -1772,10 +1772,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="O22" t="s">
         <v>177</v>
@@ -1834,10 +1834,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="N23" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="O23" t="s">
         <v>177</v>
@@ -1896,10 +1896,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="N24" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="O24" t="s">
         <v>177</v>
@@ -1934,10 +1934,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N25" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="O25" t="s">
         <v>177</v>
@@ -1972,10 +1972,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="N26" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="O26" t="s">
         <v>177</v>
@@ -2010,10 +2010,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="N27" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="O27" t="s">
         <v>177</v>
@@ -2048,10 +2048,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="N28" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="O28" t="s">
         <v>177</v>
@@ -2086,10 +2086,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="O29" t="s">
         <v>177</v>
@@ -2124,10 +2124,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="N30" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="O30" t="s">
         <v>177</v>
@@ -2162,10 +2162,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="N31" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="O31" t="s">
         <v>177</v>
@@ -2200,10 +2200,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="N32" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="O32" t="s">
         <v>177</v>
@@ -2238,10 +2238,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="N33" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="O33" t="s">
         <v>177</v>
@@ -2276,10 +2276,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="N34" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="O34" t="s">
         <v>177</v>
@@ -2314,10 +2314,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="N35" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="O35" t="s">
         <v>177</v>
@@ -2352,10 +2352,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="N36" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="O36" t="s">
         <v>177</v>
@@ -2378,10 +2378,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="N37" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="O37" t="s">
         <v>177</v>
@@ -2404,10 +2404,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="N38" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="O38" t="s">
         <v>177</v>
@@ -2430,10 +2430,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="N39" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="O39" t="s">
         <v>177</v>
@@ -2456,10 +2456,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="N40" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="O40" t="s">
         <v>177</v>
@@ -2482,10 +2482,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="N41" t="s">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="O41" t="s">
         <v>177</v>
@@ -2508,10 +2508,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="N42" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="O42" t="s">
         <v>177</v>
@@ -2534,10 +2534,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="N43" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="O43" t="s">
         <v>177</v>
@@ -2560,10 +2560,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="N44" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="O44" t="s">
         <v>177</v>
@@ -2586,10 +2586,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="N45" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="O45" t="s">
         <v>177</v>
@@ -2612,10 +2612,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="N46" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="O46" t="s">
         <v>177</v>
@@ -2638,10 +2638,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="N47" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="O47" t="s">
         <v>177</v>
@@ -2664,10 +2664,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="N48" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="O48" t="s">
         <v>177</v>
@@ -2690,10 +2690,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="N49" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="O49" t="s">
         <v>177</v>
@@ -2716,10 +2716,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="N50" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="O50" t="s">
         <v>177</v>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBA37CB-CE5C-4D5E-BB66-803B0E2BBE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A044FD2-8BEF-4B0A-BEF3-928E32B3FF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1152,10 +1152,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
         <v>177</v>
@@ -1214,10 +1214,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="N13" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="O13" t="s">
         <v>177</v>
@@ -1276,10 +1276,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="O14" t="s">
         <v>177</v>
@@ -1338,10 +1338,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O15" t="s">
         <v>177</v>
@@ -1400,10 +1400,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="N16" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="O16" t="s">
         <v>177</v>
@@ -1462,10 +1462,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="N17" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="O17" t="s">
         <v>177</v>
@@ -1524,10 +1524,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="N18" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="O18" t="s">
         <v>177</v>
@@ -1586,10 +1586,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="N19" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="O19" t="s">
         <v>177</v>
@@ -1648,10 +1648,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="N20" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="O20" t="s">
         <v>177</v>
@@ -1710,10 +1710,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="N21" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="O21" t="s">
         <v>177</v>
@@ -1772,10 +1772,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="N22" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="O22" t="s">
         <v>177</v>
@@ -1834,10 +1834,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="N23" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="O23" t="s">
         <v>177</v>
@@ -1896,10 +1896,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="N24" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="O24" t="s">
         <v>177</v>
@@ -1934,10 +1934,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="N25" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="O25" t="s">
         <v>177</v>
@@ -1972,10 +1972,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="N26" t="s">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="O26" t="s">
         <v>177</v>
@@ -2010,10 +2010,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="N27" t="s">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="O27" t="s">
         <v>177</v>
@@ -2048,10 +2048,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="N28" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="O28" t="s">
         <v>177</v>
@@ -2086,10 +2086,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="N29" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="O29" t="s">
         <v>177</v>
@@ -2124,10 +2124,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="N30" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="O30" t="s">
         <v>177</v>
@@ -2162,10 +2162,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="N31" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="O31" t="s">
         <v>177</v>
@@ -2200,10 +2200,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="N32" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="O32" t="s">
         <v>177</v>
@@ -2238,10 +2238,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="N33" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="O33" t="s">
         <v>177</v>
@@ -2276,10 +2276,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="N34" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="O34" t="s">
         <v>177</v>
@@ -2314,10 +2314,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="N35" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="O35" t="s">
         <v>177</v>
@@ -2352,10 +2352,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N36" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O36" t="s">
         <v>177</v>
@@ -2378,10 +2378,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="N37" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="O37" t="s">
         <v>177</v>
@@ -2404,10 +2404,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="N38" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="O38" t="s">
         <v>177</v>
@@ -2430,10 +2430,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="N39" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="O39" t="s">
         <v>177</v>
@@ -2456,10 +2456,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="N40" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="O40" t="s">
         <v>177</v>
@@ -2482,10 +2482,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="N41" t="s">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="O41" t="s">
         <v>177</v>
@@ -2508,10 +2508,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="N42" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="O42" t="s">
         <v>177</v>
@@ -2534,10 +2534,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="N43" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="O43" t="s">
         <v>177</v>
@@ -2560,10 +2560,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N44" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O44" t="s">
         <v>177</v>
@@ -2638,10 +2638,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="N47" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="O47" t="s">
         <v>177</v>
@@ -2690,10 +2690,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="N49" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="O49" t="s">
         <v>177</v>
@@ -2716,10 +2716,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="N50" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="O50" t="s">
         <v>177</v>
